--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1146,7 +1146,11 @@
           <t>Francisco Nixon, Jonston</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bis.org/am_office/contact.htm</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1526,7 +1530,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://acandeloria.org/</t>
+          <t>https://blog.mundo-r.com/es/festivales-galicia/</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1588,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://eternalmetal.cl/burgos-heavy-metal-2026-legion-dc/</t>
+          <t>https://metalhammer.es/burgos-heavy-metal-2026/</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2674,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://interestelarsevilla.com/</t>
+          <t>https://www.sevillaactualidad.com/cultura/593284-todo-lo-que-debes-saber-de-interestelar-sevilla-2026-artistas-horarios-y-desvios-en-las-lineas-de-autobuses/</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2736,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://metalkings.org/reports/10044</t>
+          <t>https://es.concerts-metal.com/concert_-_Metal_Strike_Fest_2026-242706.html</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3046,11 @@
           <t>Evaristo, El Drogas, Reincidentes</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>https://iberiafestival.com/contacto/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3746,7 +3754,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://www.primaverasound.com/es/barcelona</t>
+          <t>https://www.primaverasound.com/es/barcelona/tickets-info-barcelona</t>
         </is>
       </c>
     </row>
@@ -4034,11 +4042,7 @@
           <t>Sexy Zebras, Carolina Durante, Ojete Calor, Siloé, Veintiuno, Brian de Calma, Depresión Sonora, El Nido, Fontán, Hoonine, Joe Crepúsculo, La Paloma</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.palenciasonora.com/cartel-palencia-sonora-2026/</t>
-        </is>
-      </c>
+      <c r="L64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4258,7 +4262,11 @@
           <t>La M.O.D.A., Barry B, La Habitación Roja, Carlos Ares, Rufus T. Firefly, BITA, Bauer, Bum Motion Club, Comandante Twin, Isaac Corrales, Marlena, Modelo</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>https://sentirbaeza.com/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4354,11 +4362,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>https://antorchasfestival.com/</t>
-        </is>
-      </c>
+      <c r="L70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5408,11 +5412,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.125.iberdrola.com/evento/iberdrola-music-festival-madrid/</t>
-        </is>
-      </c>
+      <c r="L89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>https://piratafestival.com/es/</t>
+          <t>https://piratafestival.com/es/contacto/formulario</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>https://bigsoundfestival.com/pontevedra/pontevedra</t>
+          <t>https://bigsoundfestival.com/contacto/?lang=es</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>https://monegrosfestival.com/en</t>
+          <t>https://monegrosfestival.com/es</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://movidasound.com/ediciones-anteriores/edicion-2026/</t>
+          <t>https://movidasound.com/</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,11 @@
           <t>Ben Sims, DJ Pepo, Anika Kunst, DVS1, Elli Acula, Fleur Shore, Henrik Schwarz, Luca Agnelli, Prunk, Sam Divine</t>
         </is>
       </c>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aquasella.shop/entradas</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8776,11 +8780,7 @@
           <t>Love of Lesbian, La M.O.D.A., Siloé, Ultraligera, Carlos Ares, DJ Plan B, Fontán, Ginebras, KITAI, Karavana, Melifluo, Miss Caffeina</t>
         </is>
       </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>https://festivalmediterranea.com/726-2/</t>
-        </is>
-      </c>
+      <c r="L149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>https://festivalgigante.com/</t>
+          <t>https://festivalgigante.com/contacto/</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/10/2026 22:18</t>
+          <t>17/10/2026 22:20</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11108,7 +11108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/10/2026 22:20</t>
+          <t>17/10/2026 22:21</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11108,7 +11108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/10/2026 22:21</t>
+          <t>18/10/2026 08:02</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$L$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:S191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,13 @@
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
     <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -533,6 +540,41 @@
           <t>Web</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Email festival</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Teléfono</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Promotor</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Email ayuntamiento</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tel. ayuntamiento</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Web ayuntamiento</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -595,6 +637,37 @@
           <t>https://coolturalfest.com/</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>info@coolturalfest.com</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>CRASH MUSIC S.L</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>ayto@aytoalmeria.es</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>626900000</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>http://sede.aytoalmeria.es</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -645,6 +718,29 @@
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>informacion@alhaurindelatorre.es</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>611383940</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>https://alhaurindelatorre.es</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -703,6 +799,29 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>gdeayto@villena.es</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>629909470</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.villena.es</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -763,6 +882,37 @@
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>https://rockinrace.com/</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>info@rockinrace.com</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Sleazy Records S.L</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>padron@torremolinos.es</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>952379400</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>https://sede.torremolinos.es</t>
         </is>
       </c>
     </row>
@@ -815,6 +965,21 @@
           <t>https://emac.es/contactar-emac</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>info@emac.es</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -869,6 +1034,25 @@
           <t>https://en.visitbenidorm.es/ver/7440/benidorm-fest.html/</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>benidorm@touristinfo.net</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento.org</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -931,6 +1115,25 @@
           <t>https://www.gazpatxorock.com/</t>
         </is>
       </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>info@gazpatxorock.com</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -989,6 +1192,37 @@
           <t>https://metaljournal.net/leo-jimenez-invitado-especial-de-angeles-del-infierno-en-su-festival-todos-somos-angeles-rock-fest-2026/</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>info@metaljournal.net</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>ISA CARRIO FERNÁNDEZ PEDRO JAVIER ALONSO DIEZ S.C</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>correu@badalona.cat</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>600004196</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.badalona.cat</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1043,6 +1277,21 @@
           <t>https://polarsound.es/</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>do. Valentina Q. Las mejores noches de mi vida</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1093,6 +1342,29 @@
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>11ayuntamiento@huetortajar.org</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>742477714</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>https://huetortajar.org</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1149,6 +1421,29 @@
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://www.bis.org/am_office/contact.htm</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>americas@bis.org</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
         </is>
       </c>
     </row>
@@ -1197,6 +1492,17 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1251,6 +1557,21 @@
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1309,6 +1630,29 @@
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@pealdebecerro.es</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>601562500</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pealdebecerro.es</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1363,6 +1707,29 @@
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>secretaria@benicassim.org</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>628593434</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>https://ayto.benicassim.es</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1409,6 +1776,17 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1471,6 +1849,37 @@
           <t>https://mardejavea.es/edicion/mar-de-javea-festival-2026/</t>
         </is>
       </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>info@mardejavea.com</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>MAR DE JAVEA PRODUCCIONES S.L.U</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>info@ajxabia.com</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>648015256</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ajxabia.com</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1533,6 +1942,29 @@
           <t>https://blog.mundo-r.com/es/festivales-galicia/</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>comunica_empresa@euskaltel.com</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1591,6 +2023,33 @@
           <t>https://metalhammer.es/burgos-heavy-metal-2026/</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>contacto@metalhammer.es</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>servicio010@aytoburgos.es</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>623921931</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aytoburgos.es</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1645,6 +2104,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1699,6 +2169,29 @@
           <t>https://gijonsoundfestival.com/</t>
         </is>
       </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>info@gijonsoundfestival.com</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>758064516</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gijon.es</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1749,6 +2242,17 @@
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1807,6 +2311,25 @@
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>792317685</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>https://albacete.sedipualba.es</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1867,6 +2390,29 @@
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>https://sunandsnowweekend.com/</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>agencia@sierranevadaclub.es</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>606863174</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>https://sierranevada.es</t>
         </is>
       </c>
     </row>
@@ -1923,6 +2469,33 @@
           <t>https://www.windsofagony.com/</t>
         </is>
       </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>info@windsofagony.com</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>AD ARMA PRODUCCIONES SOCIEDAD LIMITADA con domicilio e</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1985,6 +2558,25 @@
           <t>https://ritas.es/eventos/feria-de-abril-by-ritas-18-abril/?occurrence=2026-04-18</t>
         </is>
       </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>dor AREPA FEST BY RITA&amp;</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2043,6 +2635,17 @@
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2097,6 +2700,29 @@
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>info@atarfe.es</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>647164776</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atarfe.es</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2159,6 +2785,25 @@
           <t>https://allevents.in/getxo/gallarta-burdin-rock/200029984620522</t>
         </is>
       </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>privacy@allevents.in</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>tional safeguards and are permitted to Process Personal</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2213,6 +2858,33 @@
           <t>https://marenostrumfuengirola.com/</t>
         </is>
       </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>info@marenostrumfuengirola.es</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuengirola.es</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2267,6 +2939,33 @@
           <t>https://extremusika.es/</t>
         </is>
       </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>info@extremusika.es</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-caceres.es</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2325,6 +3024,25 @@
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>758064516</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gijon.es</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2387,6 +3105,21 @@
           <t>https://rocanrola.com/</t>
         </is>
       </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>APLAZAME S.L</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2449,6 +3182,29 @@
           <t>https://www.vina-rock.com/</t>
         </is>
       </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>gdpr@vina-rock.com</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2503,6 +3259,33 @@
           <t>https://elrow.com/es/events/upcoming/city/madrid</t>
         </is>
       </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>privacy@elrowfamily.com</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>ELROW GLOBAL S.L</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>concejalcultura@ayto-torrejon.es</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-torrejon.es</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2561,6 +3344,29 @@
           <t>https://toledoguiaturisticaycultural.com/toledo-beat-festival/</t>
         </is>
       </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>info.es@vivaticket.com</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>749696972</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.toledo.es</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2615,6 +3421,25 @@
           <t>https://degustafestival.es/</t>
         </is>
       </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>soporte@bracelit.es</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>dor. PROTECCIÓN DE DATOS PERSONALES</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2677,6 +3502,25 @@
           <t>https://www.sevillaactualidad.com/cultura/593284-todo-lo-que-debes-saber-de-interestelar-sevilla-2026-artistas-horarios-y-desvios-en-las-lineas-de-autobuses/</t>
         </is>
       </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>do por la Asociación Deguadaíra, y La Prensa en Andaluz</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2737,6 +3581,21 @@
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t>https://es.concerts-metal.com/concert_-_Metal_Strike_Fest_2026-242706.html</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
         </is>
       </c>
     </row>
@@ -2789,6 +3648,29 @@
           <t>https://www.mahou.es/experiencias-mahou/vibra/vibra-mahou-fest/vibra-mahou-fest-gijon/</t>
         </is>
       </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>atencionalcliente@eventim-paylogic.es</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>758064516</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gijon.es</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2847,6 +3729,21 @@
           <t>https://www.vina-rock.com/</t>
         </is>
       </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>gdpr@vina-rock.com</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
+      <c r="P42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2897,6 +3794,21 @@
           <t>https://madrilucia.com/</t>
         </is>
       </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2949,6 +3861,33 @@
       <c r="L44" s="2" t="inlineStr">
         <is>
           <t>https://delestefestival.com/</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>info@delestefestival.com</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>Music S.L</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>673661769</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bioparcvalencia.es</t>
         </is>
       </c>
     </row>
@@ -2997,6 +3936,29 @@
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>cartasaldirector@malagahoy.es</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>609721631</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>https://www.malagahoy.es</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3051,6 +4013,25 @@
           <t>https://iberiafestival.com/contacto/</t>
         </is>
       </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>info@iberiafestival.com</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento.org</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3101,6 +4082,21 @@
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3147,6 +4143,17 @@
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3209,6 +4216,25 @@
           <t>https://aiarafest.com/2026/</t>
         </is>
       </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>kaixo@aiarafest.com</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Informáticos Aplicados a Nuevas Tecnologías S.L</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3259,6 +4285,37 @@
           <t>https://fulanitafest.com/</t>
         </is>
       </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>info@fulanitafest.com</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>THE FULANITA SISTERS S.L</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuengirola.es</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3321,6 +4378,33 @@
           <t>https://www.irunarock.com/</t>
         </is>
       </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>info@irunarock.com</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>pamplona@pamplona.es</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>600961018</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pamplona.es</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3371,6 +4455,29 @@
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>sguilsor@alboloduy.es</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>800729525</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alboloduy.es</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3429,6 +4536,29 @@
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr"/>
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>webmuncipal@ayto-zaragoza.es</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>976721100</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>https://zaragoza.es</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3479,6 +4609,37 @@
           <t>https://ritmofestival.com/</t>
         </is>
       </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>info@ritmofestival.com</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr"/>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>INFORMACIÓN AL USUARIO LA MÁQUINA DE ESCRIBIR S.L</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>info@atarfe.es</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>647164776</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.atarfe.es</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3533,6 +4694,21 @@
           <t>https://springalicante.es/carolina-durante-confirmacion-navidena-de-spring-festival-2026/</t>
         </is>
       </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>info@springalicante.es</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr"/>
+      <c r="S55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3579,6 +4755,17 @@
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="3" t="inlineStr"/>
+      <c r="P56" s="3" t="inlineStr"/>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3641,6 +4828,25 @@
           <t>https://experiencesvalencia.com/love-the-90s-valencia-2026-el-festival-que-devuelve-a-valencia-a-la-decada-mas-bailada/</t>
         </is>
       </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>673661769</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bioparcvalencia.es</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3695,6 +4901,29 @@
           <t>https://nochesdelbotanico.com/</t>
         </is>
       </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>hola@nochesdelbotanico.com</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr"/>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Web está operado por y pertenece a ICON MUSIC S.L</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3757,6 +4986,25 @@
           <t>https://www.primaverasound.com/es/barcelona/tickets-info-barcelona</t>
         </is>
       </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3819,6 +5067,33 @@
           <t>https://subsonico.es/2026/informacion/</t>
         </is>
       </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>hola@subsonico.es</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr"/>
+      <c r="P60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>info@rivasciudad.es</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>600510133</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>http://sede-electronica.rivasciudad.es</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3881,6 +5156,21 @@
           <t>https://lovereggaetonmadrid.sharemusic.es/</t>
         </is>
       </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr"/>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3939,6 +5229,25 @@
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="3" t="inlineStr"/>
+      <c r="P62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3985,6 +5294,21 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr"/>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4043,6 +5367,25 @@
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr"/>
+      <c r="O64" s="3" t="inlineStr"/>
+      <c r="P64" s="3" t="inlineStr"/>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>677681354</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aytopalencia.es</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4101,6 +5444,29 @@
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr"/>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>atencionalciudadano@zamora.es</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>638914436</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zamora.es</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4151,6 +5517,17 @@
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr"/>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr"/>
+      <c r="S66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4205,6 +5582,33 @@
           <t>https://www.mallorcamagic.es/news/mallorca-festival-en-vivo-2026-the-prodigy-cypress-hill-the-libertines</t>
         </is>
       </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>info@mallorcamagic.es</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>HelloHere S.L</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4265,6 +5669,33 @@
       <c r="L68" s="2" t="inlineStr">
         <is>
           <t>https://sentirbaeza.com/</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>comunicacion@sentirbaeza.com</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>DE SERVICIOS DE LA SOCIEDAD DE LA INFORMACIÓN Y COME</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>614062616</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
         </is>
       </c>
     </row>
@@ -4317,6 +5748,21 @@
           <t>https://underseafestival.com/entradas/</t>
         </is>
       </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr"/>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento.org</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4363,6 +5809,25 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="3" t="inlineStr"/>
+      <c r="P70" s="3" t="inlineStr"/>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>792317685</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>https://albacete.sedipualba.es</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4425,6 +5890,29 @@
           <t>https://www.foroazkenarock.com/t73605p750-azkena-rock-festival-2026</t>
         </is>
       </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr"/>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>informacion@vitoria-gasteiz.org</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>664299016</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>https://sedeelectronica.vitoria-gasteiz.org</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4487,6 +5975,21 @@
           <t>https://concertsdelpinar.es/</t>
         </is>
       </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>info@concertsdelpinar.com</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr"/>
+      <c r="P72" s="3" t="inlineStr"/>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr"/>
+      <c r="S72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4549,6 +6052,29 @@
           <t>https://sonar.es/en/tickets</t>
         </is>
       </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>privacy@sonar.es</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr"/>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4599,6 +6125,17 @@
           <t>https://www.delpoblefest.com/del-poble-fest-2026-19-al-20-de-juny-a-tavernes-de-la-valldigna/</t>
         </is>
       </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="3" t="inlineStr"/>
+      <c r="P74" s="3" t="inlineStr"/>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr"/>
+      <c r="S74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4653,6 +6190,25 @@
           <t>https://nochesdelcamino.es/</t>
         </is>
       </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>info@nochesdelcamino.es</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>CRASH MUSIC S.L</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr"/>
+      <c r="S75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4699,6 +6255,29 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr"/>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>webmuncipal@ayto-zaragoza.es</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>976721100</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>https://zaragoza.es</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4757,6 +6336,21 @@
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr"/>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4807,6 +6401,21 @@
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr"/>
+      <c r="Q78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr"/>
+      <c r="S78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4865,6 +6474,29 @@
           <t>https://www.jazzvejer.com/</t>
         </is>
       </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>entradas@jazzvejer.com</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr"/>
+      <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4915,6 +6547,25 @@
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="3" t="inlineStr"/>
+      <c r="P80" s="3" t="inlineStr"/>
+      <c r="Q80" s="3" t="inlineStr"/>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4977,6 +6628,25 @@
           <t>https://observatoriofestival.com/</t>
         </is>
       </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr"/>
+      <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>614070696</t>
+        </is>
+      </c>
+      <c r="S81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5039,6 +6709,25 @@
           <t>https://musiclegendsfestival.com/en/</t>
         </is>
       </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>mlf@dekkerevents.com</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr"/>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>DEKKER EVENTS S. L</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr"/>
+      <c r="R82" s="3" t="inlineStr"/>
+      <c r="S82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5099,6 +6788,37 @@
       <c r="L83" s="2" t="inlineStr">
         <is>
           <t>https://www.conexionvalladolid.es/</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>info@conexionvalladolid.es</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>PASIÓN EVENTOS MANAGEMENT S.L</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>info@ayuntamientopinar.es</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>786273754</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="inlineStr">
+        <is>
+          <t>http://www.pinar.es</t>
         </is>
       </c>
     </row>
@@ -5147,6 +6867,21 @@
           <t>https://divinofestival.com/</t>
         </is>
       </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>hola@divinofestival.com</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr"/>
+      <c r="P84" s="3" t="inlineStr"/>
+      <c r="Q84" s="3" t="inlineStr"/>
+      <c r="R84" s="3" t="inlineStr"/>
+      <c r="S84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5201,6 +6936,33 @@
           <t>https://www.marorfest.com/</t>
         </is>
       </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>info@shiroten.es</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr"/>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@villajoyosa.es</t>
+        </is>
+      </c>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
+          <t>606882293</t>
+        </is>
+      </c>
+      <c r="S85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.villajoyosa.com</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5263,6 +7025,33 @@
           <t>https://www.musicamino.com/</t>
         </is>
       </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>info@musicamino.com</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr"/>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>do por Exa FM y La Mejor FM en CDMX y lanzado</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr"/>
+      <c r="R86" s="3" t="inlineStr">
+        <is>
+          <t>616672616</t>
+        </is>
+      </c>
+      <c r="S86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5313,6 +7102,17 @@
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr"/>
+      <c r="Q87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="inlineStr"/>
+      <c r="S87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5367,6 +7167,21 @@
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr"/>
+      <c r="Q88" s="3" t="inlineStr"/>
+      <c r="R88" s="3" t="inlineStr"/>
+      <c r="S88" s="3" t="inlineStr">
+        <is>
+          <t>https://ayuntamientohuercaldealmeria.com</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5413,6 +7228,21 @@
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="inlineStr"/>
+      <c r="S89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5463,6 +7293,29 @@
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>concello@viveiro.gal</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr">
+        <is>
+          <t>615748574</t>
+        </is>
+      </c>
+      <c r="S90" s="3" t="inlineStr">
+        <is>
+          <t>https://viveiro.gal</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5525,6 +7378,33 @@
           <t>https://polifoniksound.com/</t>
         </is>
       </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>info@polifoniksound.com</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>comunicacion@barbastro.org</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>974310150</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="inlineStr">
+        <is>
+          <t>https://barbastro.org</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5579,6 +7459,25 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr"/>
+      <c r="Q92" s="3" t="inlineStr"/>
+      <c r="R92" s="3" t="inlineStr">
+        <is>
+          <t>616365626</t>
+        </is>
+      </c>
+      <c r="S92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5637,6 +7536,29 @@
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@elbonillo.es</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>670715147</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>https://elbonillo.es</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5699,6 +7621,21 @@
           <t>https://www.barcelonarockfest.com/en/</t>
         </is>
       </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>info@barcelonarockfest.com</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr"/>
+      <c r="Q94" s="3" t="inlineStr"/>
+      <c r="R94" s="3" t="inlineStr"/>
+      <c r="S94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5757,6 +7694,25 @@
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr"/>
+      <c r="Q95" s="3" t="inlineStr"/>
+      <c r="R95" s="3" t="inlineStr">
+        <is>
+          <t>673661769</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bioparcvalencia.es</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5803,6 +7759,17 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr"/>
+      <c r="O96" s="3" t="inlineStr"/>
+      <c r="P96" s="3" t="inlineStr"/>
+      <c r="Q96" s="3" t="inlineStr"/>
+      <c r="R96" s="3" t="inlineStr"/>
+      <c r="S96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5845,6 +7812,17 @@
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr"/>
+      <c r="O97" s="3" t="inlineStr"/>
+      <c r="P97" s="3" t="inlineStr"/>
+      <c r="Q97" s="3" t="inlineStr"/>
+      <c r="R97" s="3" t="inlineStr"/>
+      <c r="S97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5899,6 +7877,37 @@
           <t>https://festivalriobabel.com/2026/</t>
         </is>
       </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>hola@festivalriobabel.com</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr"/>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>Río Babel S.L</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>info@rivasciudad.es</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>606989481</t>
+        </is>
+      </c>
+      <c r="S98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rivasciudad.es</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5953,6 +7962,37 @@
           <t>https://salorgullo.com/</t>
         </is>
       </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>info@salorgullo.com</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>Nyoman Producciones Honestas S.L</t>
+        </is>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>fiestas@ayto-salobrena.org</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>654639979</t>
+        </is>
+      </c>
+      <c r="S99" s="3" t="inlineStr">
+        <is>
+          <t>http://www.ayto-salobrena.es</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6011,6 +8051,17 @@
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr"/>
+      <c r="O100" s="3" t="inlineStr"/>
+      <c r="P100" s="3" t="inlineStr"/>
+      <c r="Q100" s="3" t="inlineStr"/>
+      <c r="R100" s="3" t="inlineStr"/>
+      <c r="S100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6065,6 +8116,29 @@
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr"/>
+      <c r="O101" s="3" t="inlineStr"/>
+      <c r="P101" s="3" t="inlineStr"/>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>canet.alcaldia@canetdemar.cat</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>937943940</t>
+        </is>
+      </c>
+      <c r="S101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canetdemar.cat</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6115,6 +8189,29 @@
           <t>https://www.culturaelejido.com/el-ejido-al-natural-2026/</t>
         </is>
       </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr"/>
+      <c r="O102" s="3" t="inlineStr"/>
+      <c r="P102" s="3" t="inlineStr"/>
+      <c r="Q102" s="3" t="inlineStr">
+        <is>
+          <t>administracion.cultura@elejido.es</t>
+        </is>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
+        <is>
+          <t>618236663</t>
+        </is>
+      </c>
+      <c r="S102" s="3" t="inlineStr">
+        <is>
+          <t>https://elejido.es</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6169,6 +8266,29 @@
           <t>https://musicosenlanaturaleza.net/</t>
         </is>
       </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr"/>
+      <c r="P103" s="3" t="inlineStr"/>
+      <c r="Q103" s="3" t="inlineStr">
+        <is>
+          <t>hoyosespino@diputacionavila.es</t>
+        </is>
+      </c>
+      <c r="R103" s="3" t="inlineStr">
+        <is>
+          <t>608100619</t>
+        </is>
+      </c>
+      <c r="S103" s="3" t="inlineStr">
+        <is>
+          <t>https://ayuntamientohoyosdelespino.es</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6231,6 +8351,33 @@
           <t>https://www.cruillabarcelona.cat/en/</t>
         </is>
       </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>festival@cruillabarcelona.cat</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="inlineStr"/>
+      <c r="P104" s="3" t="inlineStr"/>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>oac@sant-adria.net</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>698823314</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sant-adria.cat</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6281,6 +8428,17 @@
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr"/>
+      <c r="P105" s="3" t="inlineStr"/>
+      <c r="Q105" s="3" t="inlineStr"/>
+      <c r="R105" s="3" t="inlineStr"/>
+      <c r="S105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6339,6 +8497,17 @@
           <t>https://piratafestival.com/es/contacto/formulario</t>
         </is>
       </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr"/>
+      <c r="O106" s="3" t="inlineStr"/>
+      <c r="P106" s="3" t="inlineStr"/>
+      <c r="Q106" s="3" t="inlineStr"/>
+      <c r="R106" s="3" t="inlineStr"/>
+      <c r="S106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6397,6 +8566,25 @@
           <t>https://bilbaobbklive.com/en/</t>
         </is>
       </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
+          <t>hola@feverup.com</t>
+        </is>
+      </c>
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>S.A.S. A</t>
+        </is>
+      </c>
+      <c r="Q107" s="3" t="inlineStr"/>
+      <c r="R107" s="3" t="inlineStr"/>
+      <c r="S107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6459,6 +8647,29 @@
           <t>https://motorbeach.com/</t>
         </is>
       </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr"/>
+      <c r="O108" s="3" t="inlineStr"/>
+      <c r="P108" s="3" t="inlineStr"/>
+      <c r="Q108" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@vinuesa.es</t>
+        </is>
+      </c>
+      <c r="R108" s="3" t="inlineStr">
+        <is>
+          <t>733346966</t>
+        </is>
+      </c>
+      <c r="S108" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vinuesa.es</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6513,6 +8724,29 @@
           <t>https://pirineos-sur.es/</t>
         </is>
       </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>dpo@lasttour.org</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="3" t="inlineStr"/>
+      <c r="Q109" s="3" t="inlineStr"/>
+      <c r="R109" s="3" t="inlineStr">
+        <is>
+          <t>740573150</t>
+        </is>
+      </c>
+      <c r="S109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xn--sallentdegllego-wjb.es</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6575,6 +8809,17 @@
           <t>https://portamerica.es/</t>
         </is>
       </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr"/>
+      <c r="O110" s="3" t="inlineStr"/>
+      <c r="P110" s="3" t="inlineStr"/>
+      <c r="Q110" s="3" t="inlineStr"/>
+      <c r="R110" s="3" t="inlineStr"/>
+      <c r="S110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6629,6 +8874,37 @@
           <t>https://entradas2026.starlitemarbella.com/</t>
         </is>
       </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>privacidad@starliteuniverse.com</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>NECESIDAD DE FACILITAR DATOS PERSONALES. L</t>
+        </is>
+      </c>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>delegaciondecultura@marbella.es</t>
+        </is>
+      </c>
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>621368620</t>
+        </is>
+      </c>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>https://ayuntamiento.marbella.es</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6691,6 +8967,21 @@
           <t>https://www.weekendbeach.es/</t>
         </is>
       </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>enka@wildpunk.com</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="inlineStr"/>
+      <c r="P112" s="3" t="inlineStr"/>
+      <c r="Q112" s="3" t="inlineStr"/>
+      <c r="R112" s="3" t="inlineStr"/>
+      <c r="S112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6749,6 +9040,17 @@
           <t>https://tormentafestival.es/cartel/</t>
         </is>
       </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr"/>
+      <c r="P113" s="3" t="inlineStr"/>
+      <c r="Q113" s="3" t="inlineStr"/>
+      <c r="R113" s="3" t="inlineStr"/>
+      <c r="S113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6803,6 +9105,21 @@
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr"/>
+      <c r="O114" s="3" t="inlineStr"/>
+      <c r="P114" s="3" t="inlineStr"/>
+      <c r="Q114" s="3" t="inlineStr"/>
+      <c r="R114" s="3" t="inlineStr"/>
+      <c r="S114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.granada.org</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6849,6 +9166,29 @@
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr"/>
+      <c r="O115" s="3" t="inlineStr"/>
+      <c r="P115" s="3" t="inlineStr"/>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>secretariamatamala@gmail.com</t>
+        </is>
+      </c>
+      <c r="R115" s="3" t="inlineStr">
+        <is>
+          <t>613154448</t>
+        </is>
+      </c>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.matamaladealmazan.es</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6911,6 +9251,37 @@
           <t>https://comerenasturias.es/blog/boombastic-asturias-2026</t>
         </is>
       </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>info@comerenasturias.es</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="inlineStr"/>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>Pinjim Next Solutions S.L</t>
+        </is>
+      </c>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@llanera.es</t>
+        </is>
+      </c>
+      <c r="R116" s="3" t="inlineStr">
+        <is>
+          <t>734592280</t>
+        </is>
+      </c>
+      <c r="S116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.llanera.es</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6961,6 +9332,29 @@
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr"/>
+      <c r="O117" s="3" t="inlineStr"/>
+      <c r="P117" s="3" t="inlineStr"/>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>secretaria@benicassim.org</t>
+        </is>
+      </c>
+      <c r="R117" s="3" t="inlineStr">
+        <is>
+          <t>628593434</t>
+        </is>
+      </c>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>https://ayto.benicassim.es</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7023,6 +9417,25 @@
           <t>https://atlanticfest.com/entradas/</t>
         </is>
       </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>contacto@newlive.es</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="inlineStr"/>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>do por la empresa New Live Promociones Culturales s.l</t>
+        </is>
+      </c>
+      <c r="Q118" s="3" t="inlineStr"/>
+      <c r="R118" s="3" t="inlineStr"/>
+      <c r="S118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7075,6 +9488,29 @@
       <c r="L119" s="2" t="inlineStr">
         <is>
           <t>https://bigsoundfestival.com/contacto/?lang=es</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>prensa@bigsoundfestival.com</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="inlineStr"/>
+      <c r="P119" s="3" t="inlineStr"/>
+      <c r="Q119" s="3" t="inlineStr"/>
+      <c r="R119" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
         </is>
       </c>
     </row>
@@ -7123,6 +9559,21 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr"/>
+      <c r="O120" s="3" t="inlineStr"/>
+      <c r="P120" s="3" t="inlineStr"/>
+      <c r="Q120" s="3" t="inlineStr"/>
+      <c r="R120" s="3" t="inlineStr"/>
+      <c r="S120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sanfernando.es</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7177,6 +9628,25 @@
           <t>https://www.castelloninformacion.com/castellon-festival-musica-som-festival-hombres-g-malu-vanessa/</t>
         </is>
       </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr"/>
+      <c r="O121" s="3" t="inlineStr"/>
+      <c r="P121" s="3" t="inlineStr"/>
+      <c r="Q121" s="3" t="inlineStr"/>
+      <c r="R121" s="3" t="inlineStr">
+        <is>
+          <t>879866197</t>
+        </is>
+      </c>
+      <c r="S121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.castellonexiste.es</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7231,6 +9701,29 @@
           <t>https://magdalenaenvivo.com/</t>
         </is>
       </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>devolucionesmagdalenaenvivo2026@eventsnfc.com</t>
+        </is>
+      </c>
+      <c r="O122" s="3" t="inlineStr"/>
+      <c r="P122" s="3" t="inlineStr"/>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>adminportal@ayto-santander.es</t>
+        </is>
+      </c>
+      <c r="R122" s="3" t="inlineStr"/>
+      <c r="S122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.santander.es</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7281,6 +9774,29 @@
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr"/>
+      <c r="O123" s="3" t="inlineStr"/>
+      <c r="P123" s="3" t="inlineStr"/>
+      <c r="Q123" s="3" t="inlineStr">
+        <is>
+          <t>cartasaldirector@malagahoy.es</t>
+        </is>
+      </c>
+      <c r="R123" s="3" t="inlineStr">
+        <is>
+          <t>609721631</t>
+        </is>
+      </c>
+      <c r="S123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.malagahoy.es</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7339,6 +9855,25 @@
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr"/>
+      <c r="O124" s="3" t="inlineStr"/>
+      <c r="P124" s="3" t="inlineStr"/>
+      <c r="Q124" s="3" t="inlineStr"/>
+      <c r="R124" s="3" t="inlineStr">
+        <is>
+          <t>609209742</t>
+        </is>
+      </c>
+      <c r="S124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuentelsazdesoria.es</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7401,6 +9936,21 @@
           <t>https://www.parallelfestival.com/</t>
         </is>
       </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>booking@parallelfestival.com</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="inlineStr"/>
+      <c r="P125" s="3" t="inlineStr"/>
+      <c r="Q125" s="3" t="inlineStr"/>
+      <c r="R125" s="3" t="inlineStr"/>
+      <c r="S125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7463,6 +10013,33 @@
           <t>https://sharefestival.org/</t>
         </is>
       </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>info@sharefestival.org</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="inlineStr"/>
+      <c r="P126" s="3" t="inlineStr"/>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>oac@sant-adria.net</t>
+        </is>
+      </c>
+      <c r="R126" s="3" t="inlineStr">
+        <is>
+          <t>698823314</t>
+        </is>
+      </c>
+      <c r="S126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sant-adria.cat</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7521,6 +10098,25 @@
           <t>https://www.vendavalfest.com/</t>
         </is>
       </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr"/>
+      <c r="O127" s="3" t="inlineStr"/>
+      <c r="P127" s="3" t="inlineStr"/>
+      <c r="Q127" s="3" t="inlineStr"/>
+      <c r="R127" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7583,6 +10179,25 @@
           <t>https://monegrosfestival.com/es</t>
         </is>
       </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr"/>
+      <c r="O128" s="3" t="inlineStr"/>
+      <c r="P128" s="3" t="inlineStr"/>
+      <c r="Q128" s="3" t="inlineStr"/>
+      <c r="R128" s="3" t="inlineStr">
+        <is>
+          <t>658241465</t>
+        </is>
+      </c>
+      <c r="S128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fraga.org</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7645,6 +10260,21 @@
           <t>https://arenalsound.com/en/info/contact/</t>
         </is>
       </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr"/>
+      <c r="P129" s="3" t="inlineStr"/>
+      <c r="Q129" s="3" t="inlineStr"/>
+      <c r="R129" s="3" t="inlineStr"/>
+      <c r="S129" s="3" t="inlineStr">
+        <is>
+          <t>https://burriana.es</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7707,6 +10337,25 @@
           <t>https://www.sonriasbaixas.info/</t>
         </is>
       </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr"/>
+      <c r="O130" s="3" t="inlineStr"/>
+      <c r="P130" s="3" t="inlineStr"/>
+      <c r="Q130" s="3" t="inlineStr"/>
+      <c r="R130" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7769,6 +10418,25 @@
           <t>https://www.abejarock.com/</t>
         </is>
       </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>hola@abejarock.com</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr"/>
+      <c r="P131" s="3" t="inlineStr"/>
+      <c r="Q131" s="3" t="inlineStr"/>
+      <c r="R131" s="3" t="inlineStr"/>
+      <c r="S131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aytobejar.com</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7831,6 +10499,33 @@
           <t>https://centenerarock.es/</t>
         </is>
       </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>centenerarock@gmail.com</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr"/>
+      <c r="P132" s="3" t="inlineStr"/>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>admon@aldeacentenera.es</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="inlineStr">
+        <is>
+          <t>723100746</t>
+        </is>
+      </c>
+      <c r="S132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aldeacentenera.es</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7883,6 +10578,29 @@
       <c r="L133" s="2" t="inlineStr">
         <is>
           <t>https://www.dreambeach.es/</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>contacto@dreambeach.es</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr"/>
+      <c r="P133" s="3" t="inlineStr"/>
+      <c r="Q133" s="3" t="inlineStr"/>
+      <c r="R133" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
         </is>
       </c>
     </row>
@@ -7935,6 +10653,33 @@
           <t>https://festivalamante.org/</t>
         </is>
       </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>ventanillaunica@borja.es</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr"/>
+      <c r="P134" s="3" t="inlineStr"/>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>ventanillaunica@borja.es</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>664054866</t>
+        </is>
+      </c>
+      <c r="S134" s="3" t="inlineStr">
+        <is>
+          <t>https://borja.cumpletransparencia.es</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7985,6 +10730,25 @@
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr"/>
+      <c r="O135" s="3" t="inlineStr"/>
+      <c r="P135" s="3" t="inlineStr"/>
+      <c r="Q135" s="3" t="inlineStr"/>
+      <c r="R135" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8035,6 +10799,25 @@
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr"/>
+      <c r="O136" s="3" t="inlineStr"/>
+      <c r="P136" s="3" t="inlineStr"/>
+      <c r="Q136" s="3" t="inlineStr"/>
+      <c r="R136" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S136" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8089,6 +10872,33 @@
           <t>https://www.marbella-sanpedro.com/tag/bella-festival-2026/</t>
         </is>
       </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>marbellasanpedro@gmail.com</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr"/>
+      <c r="P137" s="3" t="inlineStr"/>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>delegaciondecultura@marbella.es</t>
+        </is>
+      </c>
+      <c r="R137" s="3" t="inlineStr">
+        <is>
+          <t>621368620</t>
+        </is>
+      </c>
+      <c r="S137" s="3" t="inlineStr">
+        <is>
+          <t>https://ayuntamiento.marbella.es</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8147,6 +10957,29 @@
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr"/>
+      <c r="O138" s="3" t="inlineStr"/>
+      <c r="P138" s="3" t="inlineStr"/>
+      <c r="Q138" s="3" t="inlineStr">
+        <is>
+          <t>gdeayto@villena.es</t>
+        </is>
+      </c>
+      <c r="R138" s="3" t="inlineStr">
+        <is>
+          <t>629909470</t>
+        </is>
+      </c>
+      <c r="S138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.villena.es</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8205,6 +11038,29 @@
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr"/>
+      <c r="O139" s="3" t="inlineStr"/>
+      <c r="P139" s="3" t="inlineStr"/>
+      <c r="Q139" s="3" t="inlineStr">
+        <is>
+          <t>info@aranda.uned.es</t>
+        </is>
+      </c>
+      <c r="R139" s="3" t="inlineStr">
+        <is>
+          <t>605200034</t>
+        </is>
+      </c>
+      <c r="S139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arandadeduero.es</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8267,6 +11123,17 @@
           <t>https://thejuergasrockfestival.com/</t>
         </is>
       </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr"/>
+      <c r="O140" s="3" t="inlineStr"/>
+      <c r="P140" s="3" t="inlineStr"/>
+      <c r="Q140" s="3" t="inlineStr"/>
+      <c r="R140" s="3" t="inlineStr"/>
+      <c r="S140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8317,6 +11184,33 @@
           <t>https://prestosofest.com/</t>
         </is>
       </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>info@prestosofest.com</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr"/>
+      <c r="P141" s="3" t="inlineStr"/>
+      <c r="Q141" s="3" t="inlineStr">
+        <is>
+          <t>casaculturapo@ayto-cnarcea.es</t>
+        </is>
+      </c>
+      <c r="R141" s="3" t="inlineStr">
+        <is>
+          <t>600651771</t>
+        </is>
+      </c>
+      <c r="S141" s="3" t="inlineStr">
+        <is>
+          <t>https://cangas-del-narcea.vivirasturias.com</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8375,6 +11269,33 @@
           <t>https://brunchelectronikfestival.com/en/</t>
         </is>
       </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>info@brunchelectronik.com</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr"/>
+      <c r="P142" s="3" t="inlineStr"/>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>oac@sant-adria.net</t>
+        </is>
+      </c>
+      <c r="R142" s="3" t="inlineStr">
+        <is>
+          <t>698823314</t>
+        </is>
+      </c>
+      <c r="S142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sant-adria.cat</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8429,6 +11350,25 @@
           <t>https://camarzius.es/</t>
         </is>
       </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>info@camarzius.es</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="inlineStr"/>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>ICARUS HOLISTIC SERVICE S.L</t>
+        </is>
+      </c>
+      <c r="Q143" s="3" t="inlineStr"/>
+      <c r="R143" s="3" t="inlineStr"/>
+      <c r="S143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8483,6 +11423,25 @@
           <t>https://movidasound.com/</t>
         </is>
       </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr"/>
+      <c r="O144" s="3" t="inlineStr"/>
+      <c r="P144" s="3" t="inlineStr"/>
+      <c r="Q144" s="3" t="inlineStr"/>
+      <c r="R144" s="3" t="inlineStr">
+        <is>
+          <t>791536509</t>
+        </is>
+      </c>
+      <c r="S144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.barbate.es</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8541,6 +11500,17 @@
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr"/>
+      <c r="O145" s="3" t="inlineStr"/>
+      <c r="P145" s="3" t="inlineStr"/>
+      <c r="Q145" s="3" t="inlineStr"/>
+      <c r="R145" s="3" t="inlineStr"/>
+      <c r="S145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8603,6 +11573,21 @@
           <t>https://traskarock.com/</t>
         </is>
       </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>jorge@elhombremusic.com</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr"/>
+      <c r="P146" s="3" t="inlineStr"/>
+      <c r="Q146" s="3" t="inlineStr"/>
+      <c r="R146" s="3" t="inlineStr"/>
+      <c r="S146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8661,6 +11646,29 @@
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr"/>
+      <c r="O147" s="3" t="inlineStr"/>
+      <c r="P147" s="3" t="inlineStr"/>
+      <c r="Q147" s="3" t="inlineStr">
+        <is>
+          <t>info@inlandlapinilladh.com</t>
+        </is>
+      </c>
+      <c r="R147" s="3" t="inlineStr">
+        <is>
+          <t>602030933</t>
+        </is>
+      </c>
+      <c r="S147" s="3" t="inlineStr">
+        <is>
+          <t>https://lapinilla.es</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8723,6 +11731,17 @@
           <t>https://www.aquasella.shop/entradas</t>
         </is>
       </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr"/>
+      <c r="O148" s="3" t="inlineStr"/>
+      <c r="P148" s="3" t="inlineStr"/>
+      <c r="Q148" s="3" t="inlineStr"/>
+      <c r="R148" s="3" t="inlineStr"/>
+      <c r="S148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8781,6 +11800,17 @@
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr"/>
+      <c r="O149" s="3" t="inlineStr"/>
+      <c r="P149" s="3" t="inlineStr"/>
+      <c r="Q149" s="3" t="inlineStr"/>
+      <c r="R149" s="3" t="inlineStr"/>
+      <c r="S149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8839,6 +11869,25 @@
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr"/>
+      <c r="O150" s="3" t="inlineStr"/>
+      <c r="P150" s="3" t="inlineStr"/>
+      <c r="Q150" s="3" t="inlineStr"/>
+      <c r="R150" s="3" t="inlineStr">
+        <is>
+          <t>792317680</t>
+        </is>
+      </c>
+      <c r="S150" s="3" t="inlineStr">
+        <is>
+          <t>https://cullera.sedipualba.es</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8897,6 +11946,25 @@
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr"/>
+      <c r="O151" s="3" t="inlineStr"/>
+      <c r="P151" s="3" t="inlineStr"/>
+      <c r="Q151" s="3" t="inlineStr"/>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>649194451</t>
+        </is>
+      </c>
+      <c r="S151" s="3" t="inlineStr">
+        <is>
+          <t>https://penarroyapueblonuevo.es</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8951,6 +12019,17 @@
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr"/>
+      <c r="O152" s="3" t="inlineStr"/>
+      <c r="P152" s="3" t="inlineStr"/>
+      <c r="Q152" s="3" t="inlineStr"/>
+      <c r="R152" s="3" t="inlineStr"/>
+      <c r="S152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8997,6 +12076,29 @@
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr"/>
+      <c r="O153" s="3" t="inlineStr"/>
+      <c r="P153" s="3" t="inlineStr"/>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-aviles.es</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>653394078</t>
+        </is>
+      </c>
+      <c r="S153" s="3" t="inlineStr">
+        <is>
+          <t>https://aviles.es</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9051,6 +12153,29 @@
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr"/>
+      <c r="O154" s="3" t="inlineStr"/>
+      <c r="P154" s="3" t="inlineStr"/>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>delegadodeprotecciondedatos@cadiz.es</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>792310488</t>
+        </is>
+      </c>
+      <c r="S154" s="3" t="inlineStr">
+        <is>
+          <t>https://institucional.cadiz.es</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9105,6 +12230,37 @@
           <t>https://rototomsunsplash.com/</t>
         </is>
       </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
+          <t>gdpr@rototom.com</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="inlineStr"/>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>Rototom S.L</t>
+        </is>
+      </c>
+      <c r="Q155" s="3" t="inlineStr">
+        <is>
+          <t>secretaria@benicassim.org</t>
+        </is>
+      </c>
+      <c r="R155" s="3" t="inlineStr">
+        <is>
+          <t>628593434</t>
+        </is>
+      </c>
+      <c r="S155" s="3" t="inlineStr">
+        <is>
+          <t>https://ayto.benicassim.es</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9167,6 +12323,37 @@
           <t>https://www.flamencoonfire.com/</t>
         </is>
       </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
+          <t>info@flamencoonfire.org</t>
+        </is>
+      </c>
+      <c r="O156" s="3" t="inlineStr"/>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>o explota, directa o indirectamente. Además, FOF recoge</t>
+        </is>
+      </c>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@viana.es</t>
+        </is>
+      </c>
+      <c r="R156" s="3" t="inlineStr">
+        <is>
+          <t>609110179</t>
+        </is>
+      </c>
+      <c r="S156" s="3" t="inlineStr">
+        <is>
+          <t>http://www.viana.es</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9217,6 +12404,17 @@
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr"/>
+      <c r="O157" s="3" t="inlineStr"/>
+      <c r="P157" s="3" t="inlineStr"/>
+      <c r="Q157" s="3" t="inlineStr"/>
+      <c r="R157" s="3" t="inlineStr"/>
+      <c r="S157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9267,6 +12465,33 @@
           <t>https://rioverbena.com/</t>
         </is>
       </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>entradas@rioverbena.com</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="inlineStr"/>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>RIO VERBENA S.L</t>
+        </is>
+      </c>
+      <c r="Q158" s="3" t="inlineStr"/>
+      <c r="R158" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9321,6 +12546,29 @@
           <t>https://festivalgigante.com/contacto/</t>
         </is>
       </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr"/>
+      <c r="O159" s="3" t="inlineStr"/>
+      <c r="P159" s="3" t="inlineStr"/>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>cultura.escuelasmunicipales@aytoguadalajara.es</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="inlineStr">
+        <is>
+          <t>949887070</t>
+        </is>
+      </c>
+      <c r="S159" s="3" t="inlineStr">
+        <is>
+          <t>https://www.guadalajara.es</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9379,6 +12627,33 @@
           <t>https://sunandthunderfest.com/el-recinto/</t>
         </is>
       </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
+          <t>info@zliverock.com</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="inlineStr"/>
+      <c r="P160" s="3" t="inlineStr"/>
+      <c r="Q160" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R160" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
+      <c r="S160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fuengirola.es</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9429,6 +12704,17 @@
       </c>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr"/>
+      <c r="O161" s="3" t="inlineStr"/>
+      <c r="P161" s="3" t="inlineStr"/>
+      <c r="Q161" s="3" t="inlineStr"/>
+      <c r="R161" s="3" t="inlineStr"/>
+      <c r="S161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9487,6 +12773,29 @@
           <t>https://www.ripolletrockfestival.com/</t>
         </is>
       </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>ripolletrock97@yahoo.es</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="inlineStr"/>
+      <c r="P162" s="3" t="inlineStr"/>
+      <c r="Q162" s="3" t="inlineStr"/>
+      <c r="R162" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S162" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9549,6 +12858,37 @@
           <t>https://rocknblues.es/</t>
         </is>
       </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>info@pilpa.es</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="inlineStr"/>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>Pilpa Producciones</t>
+        </is>
+      </c>
+      <c r="Q163" s="3" t="inlineStr">
+        <is>
+          <t>direccion@downdonbenito.es</t>
+        </is>
+      </c>
+      <c r="R163" s="3" t="inlineStr">
+        <is>
+          <t>674085843</t>
+        </is>
+      </c>
+      <c r="S163" s="3" t="inlineStr">
+        <is>
+          <t>https://www.downdonbenito.es</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9603,6 +12943,29 @@
       </c>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr"/>
+      <c r="O164" s="3" t="inlineStr"/>
+      <c r="P164" s="3" t="inlineStr"/>
+      <c r="Q164" s="3" t="inlineStr">
+        <is>
+          <t>webmaster@ayto-navia.es</t>
+        </is>
+      </c>
+      <c r="R164" s="3" t="inlineStr">
+        <is>
+          <t>723194526</t>
+        </is>
+      </c>
+      <c r="S164" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-navia.es</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9657,6 +13020,29 @@
           <t>https://beltzaweekend.com/</t>
         </is>
       </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr"/>
+      <c r="O165" s="3" t="inlineStr"/>
+      <c r="P165" s="3" t="inlineStr"/>
+      <c r="Q165" s="3" t="inlineStr">
+        <is>
+          <t>pamplona@pamplona.es</t>
+        </is>
+      </c>
+      <c r="R165" s="3" t="inlineStr">
+        <is>
+          <t>600961018</t>
+        </is>
+      </c>
+      <c r="S165" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pamplona.es</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9711,6 +13097,25 @@
           <t>https://nochesdelamaestranza.com/</t>
         </is>
       </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
+          <t>grupoconcerttour@grupoconcerttour.com</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="inlineStr"/>
+      <c r="P166" s="3" t="inlineStr"/>
+      <c r="Q166" s="3" t="inlineStr"/>
+      <c r="R166" s="3" t="inlineStr"/>
+      <c r="S166" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -9767,6 +13172,33 @@
       <c r="L167" s="2" t="inlineStr">
         <is>
           <t>https://ebrovision.com/contacto/</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>hola@ebrovision.com</t>
+        </is>
+      </c>
+      <c r="O167" s="3" t="inlineStr"/>
+      <c r="P167" s="3" t="inlineStr"/>
+      <c r="Q167" s="3" t="inlineStr">
+        <is>
+          <t>buzon@mirandadeebro.es</t>
+        </is>
+      </c>
+      <c r="R167" s="3" t="inlineStr">
+        <is>
+          <t>626900413</t>
+        </is>
+      </c>
+      <c r="S167" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mirandadeebro.es</t>
         </is>
       </c>
     </row>
@@ -9819,6 +13251,17 @@
           <t>https://b-sidefestival.com/</t>
         </is>
       </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr"/>
+      <c r="O168" s="3" t="inlineStr"/>
+      <c r="P168" s="3" t="inlineStr"/>
+      <c r="Q168" s="3" t="inlineStr"/>
+      <c r="R168" s="3" t="inlineStr"/>
+      <c r="S168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -9881,6 +13324,17 @@
           <t>https://bogabogafestibala.eus/</t>
         </is>
       </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr"/>
+      <c r="O169" s="3" t="inlineStr"/>
+      <c r="P169" s="3" t="inlineStr"/>
+      <c r="Q169" s="3" t="inlineStr"/>
+      <c r="R169" s="3" t="inlineStr"/>
+      <c r="S169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9939,6 +13393,17 @@
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr"/>
+      <c r="O170" s="3" t="inlineStr"/>
+      <c r="P170" s="3" t="inlineStr"/>
+      <c r="Q170" s="3" t="inlineStr"/>
+      <c r="R170" s="3" t="inlineStr"/>
+      <c r="S170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9985,6 +13450,17 @@
       <c r="J171" s="2" t="inlineStr"/>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr"/>
+      <c r="O171" s="3" t="inlineStr"/>
+      <c r="P171" s="3" t="inlineStr"/>
+      <c r="Q171" s="3" t="inlineStr"/>
+      <c r="R171" s="3" t="inlineStr"/>
+      <c r="S171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10039,6 +13515,21 @@
           <t>https://www.hoymadrid.app/musica/20260807/brava-madrid-2026-toma-caja-magica-con-pop-moda-y-electronica/</t>
         </is>
       </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr"/>
+      <c r="O172" s="3" t="inlineStr"/>
+      <c r="P172" s="3" t="inlineStr"/>
+      <c r="Q172" s="3" t="inlineStr"/>
+      <c r="R172" s="3" t="inlineStr"/>
+      <c r="S172" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10089,6 +13580,25 @@
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr"/>
+      <c r="O173" s="3" t="inlineStr"/>
+      <c r="P173" s="3" t="inlineStr"/>
+      <c r="Q173" s="3" t="inlineStr"/>
+      <c r="R173" s="3" t="inlineStr">
+        <is>
+          <t>616972696</t>
+        </is>
+      </c>
+      <c r="S173" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayuntamiento-espana.es</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10143,6 +13653,25 @@
           <t>https://www.jardindeliciasfestival.com/madrid/</t>
         </is>
       </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>privacidad@jdld.es</t>
+        </is>
+      </c>
+      <c r="O174" s="3" t="inlineStr"/>
+      <c r="P174" s="3" t="inlineStr"/>
+      <c r="Q174" s="3" t="inlineStr"/>
+      <c r="R174" s="3" t="inlineStr"/>
+      <c r="S174" s="3" t="inlineStr">
+        <is>
+          <t>https://www.madrid.es</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10193,6 +13722,29 @@
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr"/>
+      <c r="O175" s="3" t="inlineStr"/>
+      <c r="P175" s="3" t="inlineStr"/>
+      <c r="Q175" s="3" t="inlineStr">
+        <is>
+          <t>info@carcabuey.es</t>
+        </is>
+      </c>
+      <c r="R175" s="3" t="inlineStr">
+        <is>
+          <t>738142685</t>
+        </is>
+      </c>
+      <c r="S175" s="3" t="inlineStr">
+        <is>
+          <t>https://carcabuey.es</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10255,6 +13807,25 @@
           <t>https://www.ginetarockfest.es/</t>
         </is>
       </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>ginetakamp@gmail.com</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="inlineStr"/>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>dos Alojamiento XVIII Ediciones 11 Bandas 3K Aforo máx</t>
+        </is>
+      </c>
+      <c r="Q176" s="3" t="inlineStr"/>
+      <c r="R176" s="3" t="inlineStr"/>
+      <c r="S176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10317,6 +13888,29 @@
           <t>https://piratafestival.com/es/madrid/entradas</t>
         </is>
       </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr"/>
+      <c r="O177" s="3" t="inlineStr"/>
+      <c r="P177" s="3" t="inlineStr"/>
+      <c r="Q177" s="3" t="inlineStr">
+        <is>
+          <t>info@rivasciudad.es</t>
+        </is>
+      </c>
+      <c r="R177" s="3" t="inlineStr">
+        <is>
+          <t>600510133</t>
+        </is>
+      </c>
+      <c r="S177" s="3" t="inlineStr">
+        <is>
+          <t>http://sede-electronica.rivasciudad.es</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10371,6 +13965,25 @@
           <t>https://sonoramariberaibiza.es/entradas/</t>
         </is>
       </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>tickets@sonorama-aranda.com</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="inlineStr"/>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>ÚBLICA NO PERMANENTE MAYOR. EL PLANETA SONORO S.L</t>
+        </is>
+      </c>
+      <c r="Q178" s="3" t="inlineStr"/>
+      <c r="R178" s="3" t="inlineStr"/>
+      <c r="S178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10433,6 +14046,25 @@
           <t>https://caplafestival.com/</t>
         </is>
       </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
+          <t>info@caplafestival.com</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="inlineStr"/>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>Toma Música S.L</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="inlineStr"/>
+      <c r="R179" s="3" t="inlineStr"/>
+      <c r="S179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10483,6 +14115,17 @@
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr"/>
+      <c r="O180" s="3" t="inlineStr"/>
+      <c r="P180" s="3" t="inlineStr"/>
+      <c r="Q180" s="3" t="inlineStr"/>
+      <c r="R180" s="3" t="inlineStr"/>
+      <c r="S180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10545,6 +14188,37 @@
           <t>https://festivalotonoysal.es/</t>
         </is>
       </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
+          <t>info@festivalotonoysal.es</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="inlineStr"/>
+      <c r="P181" s="3" t="inlineStr">
+        <is>
+          <t>CRASH MUSIC S.L</t>
+        </is>
+      </c>
+      <c r="Q181" s="3" t="inlineStr">
+        <is>
+          <t>info@nijar.es</t>
+        </is>
+      </c>
+      <c r="R181" s="3" t="inlineStr">
+        <is>
+          <t>618693082</t>
+        </is>
+      </c>
+      <c r="S181" s="3" t="inlineStr">
+        <is>
+          <t>https://nijar.es</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10595,6 +14269,17 @@
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr"/>
+      <c r="O182" s="3" t="inlineStr"/>
+      <c r="P182" s="3" t="inlineStr"/>
+      <c r="Q182" s="3" t="inlineStr"/>
+      <c r="R182" s="3" t="inlineStr"/>
+      <c r="S182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10645,6 +14330,37 @@
           <t>https://contempopranea.com/</t>
         </is>
       </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
+          <t>info@contempopranea.com</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="inlineStr"/>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>CRASH MUSIC S.L</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr">
+        <is>
+          <t>direccion@downdonbenito.es</t>
+        </is>
+      </c>
+      <c r="R183" s="3" t="inlineStr">
+        <is>
+          <t>674085843</t>
+        </is>
+      </c>
+      <c r="S183" s="3" t="inlineStr">
+        <is>
+          <t>https://www.downdonbenito.es</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10695,6 +14411,25 @@
           <t>https://www.jardindeliciasfestival.com/sevilla/</t>
         </is>
       </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>por confirmar</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>privacidad@jdld.es</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="inlineStr"/>
+      <c r="P184" s="3" t="inlineStr"/>
+      <c r="Q184" s="3" t="inlineStr"/>
+      <c r="R184" s="3" t="inlineStr"/>
+      <c r="S184" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10757,6 +14492,37 @@
           <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
         </is>
       </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>dpo@mediaprogramas.com</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="inlineStr"/>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>En Mediaprogramas S.L</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-caceres.es</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10819,6 +14585,33 @@
           <t>https://castanhazo.com/venda-de-entradas/</t>
         </is>
       </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="inlineStr"/>
+      <c r="P186" s="3" t="inlineStr"/>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10877,6 +14670,25 @@
           <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
         </is>
       </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
+      <c r="O187" s="3" t="inlineStr"/>
+      <c r="P187" s="3" t="inlineStr"/>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr"/>
+      <c r="S187" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10931,6 +14743,25 @@
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr"/>
+      <c r="O188" s="3" t="inlineStr"/>
+      <c r="P188" s="3" t="inlineStr"/>
+      <c r="Q188" s="3" t="inlineStr"/>
+      <c r="R188" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S188" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10981,6 +14812,25 @@
           <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
         </is>
       </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="inlineStr"/>
+      <c r="P189" s="3" t="inlineStr"/>
+      <c r="Q189" s="3" t="inlineStr"/>
+      <c r="R189" s="3" t="inlineStr"/>
+      <c r="S189" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11027,6 +14877,25 @@
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr"/>
+      <c r="O190" s="3" t="inlineStr"/>
+      <c r="P190" s="3" t="inlineStr"/>
+      <c r="Q190" s="3" t="inlineStr"/>
+      <c r="R190" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S190" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -11073,9 +14942,28 @@
       <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr"/>
+      <c r="O191" s="3" t="inlineStr"/>
+      <c r="P191" s="3" t="inlineStr"/>
+      <c r="Q191" s="3" t="inlineStr"/>
+      <c r="R191" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S191" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L191"/>
+  <autoFilter ref="A1:S191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S191"/>
+  <dimension ref="A1:S195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7457,7 +7457,11 @@
           <t>CANO, DAVS, JUNNIO</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Vida Festival</t>
+        </is>
+      </c>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7466,7 +7470,11 @@
       </c>
       <c r="N92" s="3" t="inlineStr"/>
       <c r="O92" s="3" t="inlineStr"/>
-      <c r="P92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>Sitback Produccions, S.L.</t>
+        </is>
+      </c>
       <c r="Q92" s="3" t="inlineStr"/>
       <c r="R92" s="3" t="inlineStr">
         <is>
@@ -14434,155 +14442,123 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Horteralia Cáceres 2026</t>
+          <t>Festa Presentació Vida Festival 2027: La Publicitat &amp; Bernal</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Cáceres</t>
+          <t>Antiga Fàbrica Estrella Damm</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr">
-        <is>
-          <t>CANO, CUPIDO, CYRIL KAMER</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
-        </is>
-      </c>
+          <t>Vida Records &amp; Friends, Vida Festival</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N185" s="3" t="inlineStr">
-        <is>
-          <t>dpo@mediaprogramas.com</t>
-        </is>
-      </c>
+      <c r="N185" s="3" t="inlineStr"/>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="3" t="inlineStr">
         <is>
-          <t>En Mediaprogramas S.L</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-caceres.es</t>
-        </is>
-      </c>
-      <c r="R185" s="3" t="inlineStr">
-        <is>
-          <t>618380445</t>
-        </is>
-      </c>
-      <c r="S185" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayto-caceres.es</t>
-        </is>
-      </c>
+          <t>Sitback Produccions, S.L.</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr"/>
+      <c r="R185" s="3" t="inlineStr"/>
+      <c r="S185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>Horteralia Cáceres 2026</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Recinto Ferial de Cáceres</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Cáceres</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
+          <t>Cáceres</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Urbano, Pop, Rock, Punk</t>
+          <t>Pop</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
+          <t>medio</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
+          <t>CANO, CUPIDO, CYRIL KAMER</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
+          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -14592,82 +14568,90 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>attcliente@woutick.es</t>
+          <t>dpo@mediaprogramas.com</t>
         </is>
       </c>
       <c r="O186" s="3" t="inlineStr"/>
-      <c r="P186" s="3" t="inlineStr"/>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>En Mediaprogramas S.L</t>
+        </is>
+      </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
-          <t>concello@concellodechantada.es</t>
+          <t>informacion@ayto-caceres.es</t>
         </is>
       </c>
       <c r="R186" s="3" t="inlineStr">
         <is>
-          <t>614817558</t>
+          <t>618380445</t>
         </is>
       </c>
       <c r="S186" s="3" t="inlineStr">
         <is>
-          <t>https://www.concellodechantada.org</t>
+          <t>https://www.ayto-caceres.es</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
+          <t>Chantada</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lugo</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Comunidad Valenciana</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Urbano, Pop, Rock, Punk</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
         </is>
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -14677,71 +14661,71 @@
       </c>
       <c r="N187" s="3" t="inlineStr">
         <is>
-          <t>salamatadero@gmail.com</t>
+          <t>attcliente@woutick.es</t>
         </is>
       </c>
       <c r="O187" s="3" t="inlineStr"/>
       <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="3" t="inlineStr"/>
-      <c r="R187" s="3" t="inlineStr"/>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
       <c r="S187" s="3" t="inlineStr">
         <is>
-          <t>https://www.ayora.es</t>
+          <t>https://www.concellodechantada.org</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
-      <c r="K188" s="2" t="inlineStr"/>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Lion Rock Fest</t>
+        </is>
+      </c>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
@@ -14750,55 +14734,47 @@
       </c>
       <c r="N188" s="3" t="inlineStr"/>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="3" t="inlineStr"/>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+        </is>
+      </c>
       <c r="Q188" s="3" t="inlineStr"/>
-      <c r="R188" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
-      <c r="S188" s="3" t="inlineStr">
-        <is>
-          <t>https://villarrobledo.com</t>
-        </is>
-      </c>
+      <c r="R188" s="3" t="inlineStr"/>
+      <c r="S188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="4" t="inlineStr">
         <is>
@@ -14806,140 +14782,156 @@
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr"/>
-      <c r="L189" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N189" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N189" s="3" t="inlineStr"/>
       <c r="O189" s="3" t="inlineStr"/>
-      <c r="P189" s="3" t="inlineStr"/>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>Live Nation España S.A.U.</t>
+        </is>
+      </c>
       <c r="Q189" s="3" t="inlineStr"/>
       <c r="R189" s="3" t="inlineStr"/>
-      <c r="S189" s="3" t="inlineStr">
-        <is>
-          <t>https://www.discoversevilla.city</t>
-        </is>
-      </c>
+      <c r="S189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ayora</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr"/>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N190" s="3" t="inlineStr"/>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr"/>
       <c r="Q190" s="3" t="inlineStr"/>
-      <c r="R190" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
+      <c r="R190" s="3" t="inlineStr"/>
       <c r="S190" s="3" t="inlineStr">
         <is>
-          <t>https://ajuntament.barcelona.cat</t>
+          <t>https://www.ayora.es</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Villarrobledo</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr"/>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
@@ -14953,17 +14945,277 @@
       <c r="Q191" s="3" t="inlineStr"/>
       <c r="R191" s="3" t="inlineStr">
         <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S191" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Interestelar Sevilla 2027</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
+      <c r="O192" s="3" t="inlineStr"/>
+      <c r="P192" s="3" t="inlineStr"/>
+      <c r="Q192" s="3" t="inlineStr"/>
+      <c r="R192" s="3" t="inlineStr"/>
+      <c r="S192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Primavera Sound Barcelona 2027</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-03</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-05</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Parc del Fòrum</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr"/>
+      <c r="O193" s="3" t="inlineStr"/>
+      <c r="P193" s="3" t="inlineStr"/>
+      <c r="Q193" s="3" t="inlineStr"/>
+      <c r="R193" s="3" t="inlineStr">
+        <is>
           <t>616401389</t>
         </is>
       </c>
-      <c r="S191" s="3" t="inlineStr">
+      <c r="S193" s="3" t="inlineStr">
         <is>
           <t>https://ajuntament.barcelona.cat</t>
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Sónar 2027</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-17</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-19</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Sónar de día - Fira Montjuïc</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr"/>
+      <c r="O194" s="3" t="inlineStr"/>
+      <c r="P194" s="3" t="inlineStr"/>
+      <c r="Q194" s="3" t="inlineStr"/>
+      <c r="R194" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S194" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Varios Recintos</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr"/>
+      <c r="O195" s="3" t="inlineStr"/>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>Matinée 2000, SLU</t>
+        </is>
+      </c>
+      <c r="Q195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="inlineStr"/>
+      <c r="S195" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S191"/>
+  <autoFilter ref="A1:S195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14996,7 +15248,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 08:02</t>
+          <t>18/10/2026 08:23</t>
         </is>
       </c>
     </row>
@@ -15007,7 +15259,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
@@ -15104,7 +15356,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -15124,7 +15376,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -15134,7 +15386,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S195"/>
+  <dimension ref="A1:S200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6063,7 +6063,11 @@
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr"/>
-      <c r="P73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>COPILOTS EVENTS, S.L.</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr"/>
       <c r="R73" s="3" t="inlineStr">
         <is>
@@ -7235,7 +7239,11 @@
       </c>
       <c r="N89" s="3" t="inlineStr"/>
       <c r="O89" s="3" t="inlineStr"/>
-      <c r="P89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THE RAVE KULTURE </t>
+        </is>
+      </c>
       <c r="Q89" s="3" t="inlineStr"/>
       <c r="R89" s="3" t="inlineStr"/>
       <c r="S89" s="3" t="inlineStr">
@@ -10672,7 +10680,11 @@
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr"/>
-      <c r="P134" s="3" t="inlineStr"/>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLUB MUTANTE </t>
+        </is>
+      </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
           <t>ventanillaunica@borja.es</t>
@@ -13266,7 +13278,11 @@
       </c>
       <c r="N168" s="3" t="inlineStr"/>
       <c r="O168" s="3" t="inlineStr"/>
-      <c r="P168" s="3" t="inlineStr"/>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>Debeat Swing</t>
+        </is>
+      </c>
       <c r="Q168" s="3" t="inlineStr"/>
       <c r="R168" s="3" t="inlineStr"/>
       <c r="S168" s="3" t="inlineStr"/>
@@ -14596,182 +14612,174 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t xml:space="preserve">Pub La chica de ayer </t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr"/>
+      <c r="G187" s="3" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N187" s="3" t="inlineStr"/>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R187" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S187" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>La chica Fest</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr"/>
+      <c r="S187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Chantada</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr"/>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Lion Rock Fest</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N188" s="3" t="inlineStr"/>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="3" t="inlineStr">
-        <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
-        </is>
-      </c>
-      <c r="Q188" s="3" t="inlineStr"/>
-      <c r="R188" s="3" t="inlineStr"/>
-      <c r="S188" s="3" t="inlineStr"/>
+      <c r="P188" s="3" t="inlineStr"/>
+      <c r="Q188" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R188" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Roig Arena</t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14784,7 +14792,7 @@
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+          <t>Lion Rock Fest</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr"/>
@@ -14797,7 +14805,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>Live Nation España S.A.U.</t>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14807,131 +14815,91 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>Comunidad Valenciana</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
+          <t>Alfajarín</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr"/>
+      <c r="G190" s="3" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="inlineStr">
-        <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
-        </is>
-      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N190" s="3" t="inlineStr">
-        <is>
-          <t>salamatadero@gmail.com</t>
-        </is>
-      </c>
+      <c r="N190" s="3" t="inlineStr"/>
       <c r="O190" s="3" t="inlineStr"/>
-      <c r="P190" s="3" t="inlineStr"/>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+        </is>
+      </c>
       <c r="Q190" s="3" t="inlineStr"/>
       <c r="R190" s="3" t="inlineStr"/>
-      <c r="S190" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayora.es</t>
-        </is>
-      </c>
+      <c r="S190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr"/>
+      <c r="G191" s="3" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
@@ -14941,55 +14909,47 @@
       </c>
       <c r="N191" s="3" t="inlineStr"/>
       <c r="O191" s="3" t="inlineStr"/>
-      <c r="P191" s="3" t="inlineStr"/>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>SIXTIES SOUND SEVILLA</t>
+        </is>
+      </c>
       <c r="Q191" s="3" t="inlineStr"/>
-      <c r="R191" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
-      <c r="S191" s="3" t="inlineStr">
-        <is>
-          <t>https://villarrobledo.com</t>
-        </is>
-      </c>
+      <c r="R191" s="3" t="inlineStr"/>
+      <c r="S191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
         <is>
@@ -14997,133 +14957,133 @@
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N192" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N192" s="3" t="inlineStr"/>
       <c r="O192" s="3" t="inlineStr"/>
-      <c r="P192" s="3" t="inlineStr"/>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>Live Nation España S.A.U.</t>
+        </is>
+      </c>
       <c r="Q192" s="3" t="inlineStr"/>
       <c r="R192" s="3" t="inlineStr"/>
-      <c r="S192" s="3" t="inlineStr">
-        <is>
-          <t>https://www.discoversevilla.city</t>
-        </is>
-      </c>
+      <c r="S192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ayora</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N193" s="3" t="inlineStr"/>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O193" s="3" t="inlineStr"/>
       <c r="P193" s="3" t="inlineStr"/>
       <c r="Q193" s="3" t="inlineStr"/>
-      <c r="R193" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
+      <c r="R193" s="3" t="inlineStr"/>
       <c r="S193" s="3" t="inlineStr">
         <is>
-          <t>https://ajuntament.barcelona.cat</t>
+          <t>https://www.ayora.es</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>NoTeMofest acto 4</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>Andén 56</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr"/>
+      <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="4" t="inlineStr">
         <is>
@@ -15140,63 +15100,67 @@
       </c>
       <c r="N194" s="3" t="inlineStr"/>
       <c r="O194" s="3" t="inlineStr"/>
-      <c r="P194" s="3" t="inlineStr"/>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>Steel Souls Producciones</t>
+        </is>
+      </c>
       <c r="Q194" s="3" t="inlineStr"/>
-      <c r="R194" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
-      <c r="S194" s="3" t="inlineStr">
-        <is>
-          <t>https://ajuntament.barcelona.cat</t>
-        </is>
-      </c>
+      <c r="R194" s="3" t="inlineStr"/>
+      <c r="S194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Varios Recintos</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Villarrobledo</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr"/>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr"/>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>Circuit Festival</t>
-        </is>
-      </c>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
@@ -15205,17 +15169,334 @@
       </c>
       <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" s="3" t="inlineStr"/>
-      <c r="P195" s="3" t="inlineStr">
+      <c r="P195" s="3" t="inlineStr"/>
+      <c r="Q195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S195" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Interestelar Sevilla 2027</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>2027-05-15</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="inlineStr"/>
+      <c r="P196" s="3" t="inlineStr"/>
+      <c r="Q196" s="3" t="inlineStr"/>
+      <c r="R196" s="3" t="inlineStr"/>
+      <c r="S196" s="3" t="inlineStr">
+        <is>
+          <t>https://www.discoversevilla.city</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Primavera Sound Barcelona 2027</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-03</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-05</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Parc del Fòrum</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr"/>
+      <c r="O197" s="3" t="inlineStr"/>
+      <c r="P197" s="3" t="inlineStr"/>
+      <c r="Q197" s="3" t="inlineStr"/>
+      <c r="R197" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S197" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Sónar 2027</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-17</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-19</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Sónar de día - Fira Montjuïc</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr"/>
+      <c r="O198" s="3" t="inlineStr"/>
+      <c r="P198" s="3" t="inlineStr"/>
+      <c r="Q198" s="3" t="inlineStr"/>
+      <c r="R198" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S198" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Varios Recintos</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr"/>
+      <c r="O199" s="3" t="inlineStr"/>
+      <c r="P199" s="3" t="inlineStr">
         <is>
           <t>Matinée 2000, SLU</t>
         </is>
       </c>
-      <c r="Q195" s="3" t="inlineStr"/>
-      <c r="R195" s="3" t="inlineStr"/>
-      <c r="S195" s="3" t="inlineStr"/>
+      <c r="Q199" s="3" t="inlineStr"/>
+      <c r="R199" s="3" t="inlineStr"/>
+      <c r="S199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Scanner bilbao</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>D8 sorkuntza</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr"/>
+      <c r="O200" s="3" t="inlineStr"/>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>Copilots Events</t>
+        </is>
+      </c>
+      <c r="Q200" s="3" t="inlineStr"/>
+      <c r="R200" s="3" t="inlineStr"/>
+      <c r="S200" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S195"/>
+  <autoFilter ref="A1:S200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15248,7 +15529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 08:23</t>
+          <t>18/10/2026 08:40</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15540,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
@@ -15269,7 +15550,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -15296,7 +15577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -15366,7 +15647,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -15376,7 +15657,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -15386,7 +15667,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -653,16 +653,8 @@
           <t>CRASH MUSIC S.L</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>ayto@aytoalmeria.es</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>626900000</t>
-        </is>
-      </c>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>http://sede.aytoalmeria.es</t>
@@ -1127,8 +1119,16 @@
       </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>880898509</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
           <t>https://www.ayora.es</t>
@@ -2035,16 +2035,8 @@
       </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>servicio010@aytoburgos.es</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>623921931</t>
-        </is>
-      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
           <t>https://www.aytoburgos.es</t>
@@ -2322,7 +2314,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792317685</t>
+          <t>792324372</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2707,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>647164776</t>
+          <t>644550455</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -4397,7 +4389,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>600961018</t>
+          <t>722515367</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4470,7 +4462,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>800729525</t>
+          <t>686165275</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4632,7 +4624,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>647164776</t>
+          <t>644550455</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5820,7 +5812,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792317685</t>
+          <t>792324372</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5905,7 +5897,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>664299016</t>
+          <t>639444225</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7316,7 +7308,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>615748574</t>
+          <t>656566497</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7405,7 +7397,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>974310150</t>
+          <t>755638228</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -10685,16 +10677,8 @@
           <t xml:space="preserve">CLUB MUTANTE </t>
         </is>
       </c>
-      <c r="Q134" s="3" t="inlineStr">
-        <is>
-          <t>ventanillaunica@borja.es</t>
-        </is>
-      </c>
-      <c r="R134" s="3" t="inlineStr">
-        <is>
-          <t>664054866</t>
-        </is>
-      </c>
+      <c r="Q134" s="3" t="inlineStr"/>
+      <c r="R134" s="3" t="inlineStr"/>
       <c r="S134" s="3" t="inlineStr">
         <is>
           <t>https://borja.cumpletransparencia.es</t>
@@ -11454,7 +11438,7 @@
       <c r="Q144" s="3" t="inlineStr"/>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>791536509</t>
+          <t>753558549</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr">
@@ -11900,7 +11884,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792317680</t>
+          <t>792324361</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12104,16 +12088,8 @@
       <c r="N153" s="3" t="inlineStr"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
-      <c r="Q153" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-aviles.es</t>
-        </is>
-      </c>
-      <c r="R153" s="3" t="inlineStr">
-        <is>
-          <t>653394078</t>
-        </is>
-      </c>
+      <c r="Q153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="inlineStr"/>
       <c r="S153" s="3" t="inlineStr">
         <is>
           <t>https://aviles.es</t>
@@ -12188,7 +12164,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792310488</t>
+          <t>787239037</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12359,16 +12335,8 @@
           <t>o explota, directa o indirectamente. Además, FOF recoge</t>
         </is>
       </c>
-      <c r="Q156" s="3" t="inlineStr">
-        <is>
-          <t>ayuntamiento@viana.es</t>
-        </is>
-      </c>
-      <c r="R156" s="3" t="inlineStr">
-        <is>
-          <t>609110179</t>
-        </is>
-      </c>
+      <c r="Q156" s="3" t="inlineStr"/>
+      <c r="R156" s="3" t="inlineStr"/>
       <c r="S156" s="3" t="inlineStr">
         <is>
           <t>http://www.viana.es</t>
@@ -13055,7 +13023,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>600961018</t>
+          <t>722515367</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13213,7 +13181,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>626900413</t>
+          <t>623262727</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -15048,8 +15016,16 @@
       </c>
       <c r="O193" s="3" t="inlineStr"/>
       <c r="P193" s="3" t="inlineStr"/>
-      <c r="Q193" s="3" t="inlineStr"/>
-      <c r="R193" s="3" t="inlineStr"/>
+      <c r="Q193" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R193" s="3" t="inlineStr">
+        <is>
+          <t>880898509</t>
+        </is>
+      </c>
       <c r="S193" s="3" t="inlineStr">
         <is>
           <t>https://www.ayora.es</t>
@@ -15529,7 +15505,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 08:40</t>
+          <t>18/10/2026 09:54</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S200"/>
+  <dimension ref="A1:S198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -653,8 +653,16 @@
           <t>CRASH MUSIC S.L</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>ayto@aytoalmeria.es</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>626900000</t>
+        </is>
+      </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>http://sede.aytoalmeria.es</t>
@@ -1119,16 +1127,8 @@
       </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>registro@ayora.es</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>880898509</t>
-        </is>
-      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
           <t>https://www.ayora.es</t>
@@ -2035,8 +2035,16 @@
       </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>servicio010@aytoburgos.es</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>623921931</t>
+        </is>
+      </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
           <t>https://www.aytoburgos.es</t>
@@ -2314,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792324372</t>
+          <t>792317685</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2707,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>644550455</t>
+          <t>647164776</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -4389,7 +4397,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>722515367</t>
+          <t>600961018</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4462,7 +4470,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>686165275</t>
+          <t>800729525</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4624,7 +4632,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>644550455</t>
+          <t>647164776</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5812,7 +5820,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792324372</t>
+          <t>792317685</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5897,7 +5905,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>639444225</t>
+          <t>664299016</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7308,7 +7316,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>656566497</t>
+          <t>615748574</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7397,7 +7405,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>755638228</t>
+          <t>974310150</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -10677,8 +10685,16 @@
           <t xml:space="preserve">CLUB MUTANTE </t>
         </is>
       </c>
-      <c r="Q134" s="3" t="inlineStr"/>
-      <c r="R134" s="3" t="inlineStr"/>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>ventanillaunica@borja.es</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>664054866</t>
+        </is>
+      </c>
       <c r="S134" s="3" t="inlineStr">
         <is>
           <t>https://borja.cumpletransparencia.es</t>
@@ -11438,7 +11454,7 @@
       <c r="Q144" s="3" t="inlineStr"/>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>753558549</t>
+          <t>791536509</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr">
@@ -11884,7 +11900,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792324361</t>
+          <t>792317680</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12088,8 +12104,16 @@
       <c r="N153" s="3" t="inlineStr"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
-      <c r="Q153" s="3" t="inlineStr"/>
-      <c r="R153" s="3" t="inlineStr"/>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-aviles.es</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>653394078</t>
+        </is>
+      </c>
       <c r="S153" s="3" t="inlineStr">
         <is>
           <t>https://aviles.es</t>
@@ -12164,7 +12188,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>787239037</t>
+          <t>792310488</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12335,8 +12359,16 @@
           <t>o explota, directa o indirectamente. Además, FOF recoge</t>
         </is>
       </c>
-      <c r="Q156" s="3" t="inlineStr"/>
-      <c r="R156" s="3" t="inlineStr"/>
+      <c r="Q156" s="3" t="inlineStr">
+        <is>
+          <t>ayuntamiento@viana.es</t>
+        </is>
+      </c>
+      <c r="R156" s="3" t="inlineStr">
+        <is>
+          <t>609110179</t>
+        </is>
+      </c>
       <c r="S156" s="3" t="inlineStr">
         <is>
           <t>http://www.viana.es</t>
@@ -13023,7 +13055,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>722515367</t>
+          <t>600961018</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13181,7 +13213,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>623262727</t>
+          <t>626900413</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14426,328 +14458,332 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Festa Presentació Vida Festival 2027: La Publicitat &amp; Bernal</t>
+          <t>Horteralia Cáceres 2026</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Antiga Fàbrica Estrella Damm</t>
+          <t>Recinto Ferial de Cáceres</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cáceres</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr"/>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Pop</t>
+        </is>
+      </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>CANO, CUPIDO, CYRIL KAMER</t>
+        </is>
+      </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Vida Records &amp; Friends, Vida Festival</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr"/>
+          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
+        </is>
+      </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N185" s="3" t="inlineStr"/>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>dpo@mediaprogramas.com</t>
+        </is>
+      </c>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="3" t="inlineStr">
         <is>
-          <t>Sitback Produccions, S.L.</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr"/>
-      <c r="R185" s="3" t="inlineStr"/>
-      <c r="S185" s="3" t="inlineStr"/>
+          <t>En Mediaprogramas S.L</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-caceres.es</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Horteralia Cáceres 2026</t>
+          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Cáceres</t>
+          <t xml:space="preserve">Pub La chica de ayer </t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>CANO, CUPIDO, CYRIL KAMER</t>
-        </is>
-      </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr">
-        <is>
-          <t>dpo@mediaprogramas.com</t>
-        </is>
-      </c>
+      <c r="N186" s="3" t="inlineStr"/>
       <c r="O186" s="3" t="inlineStr"/>
       <c r="P186" s="3" t="inlineStr">
         <is>
-          <t>En Mediaprogramas S.L</t>
-        </is>
-      </c>
-      <c r="Q186" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-caceres.es</t>
-        </is>
-      </c>
-      <c r="R186" s="3" t="inlineStr">
-        <is>
-          <t>618380445</t>
-        </is>
-      </c>
-      <c r="S186" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayto-caceres.es</t>
-        </is>
-      </c>
+          <t>La chica Fest</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr"/>
+      <c r="R186" s="3" t="inlineStr"/>
+      <c r="S186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pub La chica de ayer </t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr"/>
-      <c r="G187" s="3" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
+          <t>Chantada</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr"/>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr">
-        <is>
-          <t>La chica Fest</t>
-        </is>
-      </c>
-      <c r="Q187" s="3" t="inlineStr"/>
-      <c r="R187" s="3" t="inlineStr"/>
-      <c r="S187" s="3" t="inlineStr"/>
+      <c r="P187" s="3" t="inlineStr"/>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S187" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>Lion Rock Fest</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N188" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N188" s="3" t="inlineStr"/>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="3" t="inlineStr"/>
-      <c r="Q188" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R188" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S188" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="inlineStr"/>
+      <c r="R188" s="3" t="inlineStr"/>
+      <c r="S188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Alfajarín</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Alfajarín</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14758,11 +14794,7 @@
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>Lion Rock Fest</t>
-        </is>
-      </c>
+      <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
@@ -14773,7 +14805,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14783,7 +14815,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -14798,15 +14830,19 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr"/>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>SEVILLA</t>
+        </is>
+      </c>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
@@ -14826,7 +14862,7 @@
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+          <t>SIXTIES SOUND SEVILLA</t>
         </is>
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
@@ -14836,30 +14872,34 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>SALA EVEN</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr"/>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="4" t="inlineStr">
@@ -14868,7 +14908,11 @@
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+        </is>
+      </c>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
@@ -14879,7 +14923,7 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>SIXTIES SOUND SEVILLA</t>
+          <t>Live Nation España S.A.U.</t>
         </is>
       </c>
       <c r="Q191" s="3" t="inlineStr"/>
@@ -14889,7 +14933,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -14904,21 +14948,29 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Roig Arena</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
+          <t>Ayora</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="G192" s="3" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr"/>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
@@ -14927,146 +14979,142 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr"/>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N192" s="3" t="inlineStr"/>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O192" s="3" t="inlineStr"/>
-      <c r="P192" s="3" t="inlineStr">
-        <is>
-          <t>Live Nation España S.A.U.</t>
-        </is>
-      </c>
+      <c r="P192" s="3" t="inlineStr"/>
       <c r="Q192" s="3" t="inlineStr"/>
       <c r="R192" s="3" t="inlineStr"/>
-      <c r="S192" s="3" t="inlineStr"/>
+      <c r="S192" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>NoTeMofest acto 4</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t>Andén 56</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>Comunidad Valenciana</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr">
-        <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
-        </is>
-      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N193" s="3" t="inlineStr">
-        <is>
-          <t>salamatadero@gmail.com</t>
-        </is>
-      </c>
+      <c r="N193" s="3" t="inlineStr"/>
       <c r="O193" s="3" t="inlineStr"/>
-      <c r="P193" s="3" t="inlineStr"/>
-      <c r="Q193" s="3" t="inlineStr">
-        <is>
-          <t>registro@ayora.es</t>
-        </is>
-      </c>
-      <c r="R193" s="3" t="inlineStr">
-        <is>
-          <t>880898509</t>
-        </is>
-      </c>
-      <c r="S193" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayora.es</t>
-        </is>
-      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>Steel Souls Producciones</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="inlineStr"/>
+      <c r="R193" s="3" t="inlineStr"/>
+      <c r="S193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>NoTeMofest acto 4</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Andén 56</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr"/>
+          <t>Villarrobledo</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
@@ -15076,122 +15124,122 @@
       </c>
       <c r="N194" s="3" t="inlineStr"/>
       <c r="O194" s="3" t="inlineStr"/>
-      <c r="P194" s="3" t="inlineStr">
-        <is>
-          <t>Steel Souls Producciones</t>
-        </is>
-      </c>
+      <c r="P194" s="3" t="inlineStr"/>
       <c r="Q194" s="3" t="inlineStr"/>
-      <c r="R194" s="3" t="inlineStr"/>
-      <c r="S194" s="3" t="inlineStr"/>
+      <c r="R194" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S194" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>Interestelar Sevilla 2027</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-05-15</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N195" s="3" t="inlineStr"/>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
       <c r="O195" s="3" t="inlineStr"/>
       <c r="P195" s="3" t="inlineStr"/>
       <c r="Q195" s="3" t="inlineStr"/>
-      <c r="R195" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
+      <c r="R195" s="3" t="inlineStr"/>
       <c r="S195" s="3" t="inlineStr">
         <is>
-          <t>https://villarrobledo.com</t>
+          <t>https://www.discoversevilla.city</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>Primavera Sound Barcelona 2027</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-06-03</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Parc del Fòrum</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -15202,50 +15250,46 @@
       </c>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N196" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N196" s="3" t="inlineStr"/>
       <c r="O196" s="3" t="inlineStr"/>
       <c r="P196" s="3" t="inlineStr"/>
       <c r="Q196" s="3" t="inlineStr"/>
-      <c r="R196" s="3" t="inlineStr"/>
+      <c r="R196" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
       <c r="S196" s="3" t="inlineStr">
         <is>
-          <t>https://www.discoversevilla.city</t>
+          <t>https://ajuntament.barcelona.cat</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Sónar 2027</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Sónar de día - Fira Montjuïc</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -15295,39 +15339,35 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>Scanner bilbao</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>D8 sorkuntza</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="4" t="inlineStr">
         <is>
@@ -15344,135 +15384,17 @@
       </c>
       <c r="N198" s="3" t="inlineStr"/>
       <c r="O198" s="3" t="inlineStr"/>
-      <c r="P198" s="3" t="inlineStr"/>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>Copilots Events</t>
+        </is>
+      </c>
       <c r="Q198" s="3" t="inlineStr"/>
-      <c r="R198" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
-      <c r="S198" s="3" t="inlineStr">
-        <is>
-          <t>https://ajuntament.barcelona.cat</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>2027-08-15</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>2027-08-15</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>Varios Recintos</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr"/>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>Circuit Festival</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="2" t="inlineStr">
-        <is>
-          <t>confirmado</t>
-        </is>
-      </c>
-      <c r="N199" s="3" t="inlineStr"/>
-      <c r="O199" s="3" t="inlineStr"/>
-      <c r="P199" s="3" t="inlineStr">
-        <is>
-          <t>Matinée 2000, SLU</t>
-        </is>
-      </c>
-      <c r="Q199" s="3" t="inlineStr"/>
-      <c r="R199" s="3" t="inlineStr"/>
-      <c r="S199" s="3" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Scanner bilbao</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>D8 sorkuntza</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr"/>
-      <c r="G200" s="3" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="4" t="inlineStr">
-        <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="2" t="inlineStr">
-        <is>
-          <t>confirmado</t>
-        </is>
-      </c>
-      <c r="N200" s="3" t="inlineStr"/>
-      <c r="O200" s="3" t="inlineStr"/>
-      <c r="P200" s="3" t="inlineStr">
-        <is>
-          <t>Copilots Events</t>
-        </is>
-      </c>
-      <c r="Q200" s="3" t="inlineStr"/>
-      <c r="R200" s="3" t="inlineStr"/>
-      <c r="S200" s="3" t="inlineStr"/>
+      <c r="R198" s="3" t="inlineStr"/>
+      <c r="S198" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S200"/>
+  <autoFilter ref="A1:S198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15505,7 +15427,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 09:54</t>
+          <t>18/10/2026 13:47</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15438,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
@@ -15526,7 +15448,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -15613,7 +15535,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -15633,7 +15555,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:47</t>
+          <t>18/10/2026 13:53</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S198"/>
+  <dimension ref="A1:S200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -653,16 +653,8 @@
           <t>CRASH MUSIC S.L</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>ayto@aytoalmeria.es</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>626900000</t>
-        </is>
-      </c>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
           <t>http://sede.aytoalmeria.es</t>
@@ -814,7 +806,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>629909470</t>
+          <t>603198684</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1127,8 +1119,16 @@
       </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>880898509</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
           <t>https://www.ayora.es</t>
@@ -2035,16 +2035,8 @@
       </c>
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>servicio010@aytoburgos.es</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>623921931</t>
-        </is>
-      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
           <t>https://www.aytoburgos.es</t>
@@ -2322,7 +2314,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792317685</t>
+          <t>792410179</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2707,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>647164776</t>
+          <t>839683908</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3280,7 +3272,11 @@
           <t>concejalcultura@ayto-torrejon.es</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>800014859</t>
+        </is>
+      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4397,7 +4393,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>600961018</t>
+          <t>642255365</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4470,7 +4466,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>800729525</t>
+          <t>761193158</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4632,7 +4628,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>647164776</t>
+          <t>839683908</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5820,7 +5816,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792317685</t>
+          <t>792410179</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>664299016</t>
+          <t>640798586</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7316,7 +7312,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>615748574</t>
+          <t>639263539</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7405,7 +7401,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>974310150</t>
+          <t>633534291</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -7916,7 +7912,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>606989481</t>
+          <t>604909896</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -10685,16 +10681,8 @@
           <t xml:space="preserve">CLUB MUTANTE </t>
         </is>
       </c>
-      <c r="Q134" s="3" t="inlineStr">
-        <is>
-          <t>ventanillaunica@borja.es</t>
-        </is>
-      </c>
-      <c r="R134" s="3" t="inlineStr">
-        <is>
-          <t>664054866</t>
-        </is>
-      </c>
+      <c r="Q134" s="3" t="inlineStr"/>
+      <c r="R134" s="3" t="inlineStr"/>
       <c r="S134" s="3" t="inlineStr">
         <is>
           <t>https://borja.cumpletransparencia.es</t>
@@ -10992,7 +10980,7 @@
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>629909470</t>
+          <t>603198684</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr">
@@ -11900,7 +11888,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792317680</t>
+          <t>792410165</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12104,16 +12092,8 @@
       <c r="N153" s="3" t="inlineStr"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
-      <c r="Q153" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-aviles.es</t>
-        </is>
-      </c>
-      <c r="R153" s="3" t="inlineStr">
-        <is>
-          <t>653394078</t>
-        </is>
-      </c>
+      <c r="Q153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="inlineStr"/>
       <c r="S153" s="3" t="inlineStr">
         <is>
           <t>https://aviles.es</t>
@@ -12188,7 +12168,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792310488</t>
+          <t>792402988</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12359,16 +12339,8 @@
           <t>o explota, directa o indirectamente. Además, FOF recoge</t>
         </is>
       </c>
-      <c r="Q156" s="3" t="inlineStr">
-        <is>
-          <t>ayuntamiento@viana.es</t>
-        </is>
-      </c>
-      <c r="R156" s="3" t="inlineStr">
-        <is>
-          <t>609110179</t>
-        </is>
-      </c>
+      <c r="Q156" s="3" t="inlineStr"/>
+      <c r="R156" s="3" t="inlineStr"/>
       <c r="S156" s="3" t="inlineStr">
         <is>
           <t>http://www.viana.es</t>
@@ -12973,12 +12945,12 @@
       <c r="P164" s="3" t="inlineStr"/>
       <c r="Q164" s="3" t="inlineStr">
         <is>
-          <t>webmaster@ayto-navia.es</t>
+          <t>adl@ayto-navia.es</t>
         </is>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>723194526</t>
+          <t>734592280</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr">
@@ -13055,7 +13027,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>600961018</t>
+          <t>642255365</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -14458,332 +14430,328 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Horteralia Cáceres 2026</t>
+          <t>Festa Presentació Vida Festival 2027: La Publicitat &amp; Bernal</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Cáceres</t>
+          <t>Antiga Fàbrica Estrella Damm</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr">
-        <is>
-          <t>CANO, CUPIDO, CYRIL KAMER</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
-        </is>
-      </c>
+          <t>Vida Records &amp; Friends, Vida Festival</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N185" s="3" t="inlineStr">
-        <is>
-          <t>dpo@mediaprogramas.com</t>
-        </is>
-      </c>
+      <c r="N185" s="3" t="inlineStr"/>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="3" t="inlineStr">
         <is>
-          <t>En Mediaprogramas S.L</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-caceres.es</t>
-        </is>
-      </c>
-      <c r="R185" s="3" t="inlineStr">
-        <is>
-          <t>618380445</t>
-        </is>
-      </c>
-      <c r="S185" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayto-caceres.es</t>
-        </is>
-      </c>
+          <t>Sitback Produccions, S.L.</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr"/>
+      <c r="R185" s="3" t="inlineStr"/>
+      <c r="S185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
+          <t>Horteralia Cáceres 2026</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pub La chica de ayer </t>
+          <t>Recinto Ferial de Cáceres</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cáceres</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr"/>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Pop</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>CANO, CUPIDO, CYRIL KAMER</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>dpo@mediaprogramas.com</t>
+        </is>
+      </c>
       <c r="O186" s="3" t="inlineStr"/>
       <c r="P186" s="3" t="inlineStr">
         <is>
-          <t>La chica Fest</t>
-        </is>
-      </c>
-      <c r="Q186" s="3" t="inlineStr"/>
-      <c r="R186" s="3" t="inlineStr"/>
-      <c r="S186" s="3" t="inlineStr"/>
+          <t>En Mediaprogramas S.L</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
+      <c r="S186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-caceres.es</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t xml:space="preserve">Pub La chica de ayer </t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr"/>
+      <c r="G187" s="3" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N187" s="3" t="inlineStr"/>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R187" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S187" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>La chica Fest</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr"/>
+      <c r="S187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Chantada</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr"/>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Lion Rock Fest</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N188" s="3" t="inlineStr"/>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="3" t="inlineStr">
-        <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
-        </is>
-      </c>
-      <c r="Q188" s="3" t="inlineStr"/>
-      <c r="R188" s="3" t="inlineStr"/>
-      <c r="S188" s="3" t="inlineStr"/>
+      <c r="P188" s="3" t="inlineStr"/>
+      <c r="Q188" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R188" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S188" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14794,7 +14762,11 @@
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>Lion Rock Fest</t>
+        </is>
+      </c>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
@@ -14805,7 +14777,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14815,7 +14787,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -14830,19 +14802,15 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>SALA EVEN</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
+          <t>Alfajarín</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr"/>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
@@ -14862,7 +14830,7 @@
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr">
         <is>
-          <t>SIXTIES SOUND SEVILLA</t>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
         </is>
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
@@ -14872,34 +14840,30 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Roig Arena</t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr"/>
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="4" t="inlineStr">
@@ -14908,11 +14872,7 @@
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
-        </is>
-      </c>
+      <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
@@ -14923,7 +14883,7 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>Live Nation España S.A.U.</t>
+          <t>SIXTIES SOUND SEVILLA</t>
         </is>
       </c>
       <c r="Q191" s="3" t="inlineStr"/>
@@ -14933,7 +14893,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -14948,12 +14908,12 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -14961,16 +14921,8 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>Comunidad Valenciana</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
+      <c r="G192" s="3" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
@@ -14979,142 +14931,146 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr">
-        <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
-        </is>
-      </c>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N192" s="3" t="inlineStr">
-        <is>
-          <t>salamatadero@gmail.com</t>
-        </is>
-      </c>
+      <c r="N192" s="3" t="inlineStr"/>
       <c r="O192" s="3" t="inlineStr"/>
-      <c r="P192" s="3" t="inlineStr"/>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>Live Nation España S.A.U.</t>
+        </is>
+      </c>
       <c r="Q192" s="3" t="inlineStr"/>
       <c r="R192" s="3" t="inlineStr"/>
-      <c r="S192" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayora.es</t>
-        </is>
-      </c>
+      <c r="S192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>NoTeMofest acto 4</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Andén 56</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Ayora</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr"/>
-      <c r="K193" s="2" t="inlineStr"/>
-      <c r="L193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N193" s="3" t="inlineStr"/>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O193" s="3" t="inlineStr"/>
-      <c r="P193" s="3" t="inlineStr">
-        <is>
-          <t>Steel Souls Producciones</t>
-        </is>
-      </c>
-      <c r="Q193" s="3" t="inlineStr"/>
-      <c r="R193" s="3" t="inlineStr"/>
-      <c r="S193" s="3" t="inlineStr"/>
+      <c r="P193" s="3" t="inlineStr"/>
+      <c r="Q193" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R193" s="3" t="inlineStr">
+        <is>
+          <t>880898509</t>
+        </is>
+      </c>
+      <c r="S193" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>NoTeMofest acto 4</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>Andén 56</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr"/>
+      <c r="G194" s="3" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
@@ -15124,122 +15080,122 @@
       </c>
       <c r="N194" s="3" t="inlineStr"/>
       <c r="O194" s="3" t="inlineStr"/>
-      <c r="P194" s="3" t="inlineStr"/>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>Steel Souls Producciones</t>
+        </is>
+      </c>
       <c r="Q194" s="3" t="inlineStr"/>
-      <c r="R194" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
-      <c r="S194" s="3" t="inlineStr">
-        <is>
-          <t>https://villarrobledo.com</t>
-        </is>
-      </c>
+      <c r="R194" s="3" t="inlineStr"/>
+      <c r="S194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Villarrobledo</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr"/>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
       <c r="K195" s="2" t="inlineStr"/>
-      <c r="L195" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N195" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" s="3" t="inlineStr"/>
       <c r="P195" s="3" t="inlineStr"/>
       <c r="Q195" s="3" t="inlineStr"/>
-      <c r="R195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
       <c r="S195" s="3" t="inlineStr">
         <is>
-          <t>https://www.discoversevilla.city</t>
+          <t>https://villarrobledo.com</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Interestelar Sevilla 2027</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-05-15</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -15250,46 +15206,50 @@
       </c>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N196" s="3" t="inlineStr"/>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
       <c r="O196" s="3" t="inlineStr"/>
       <c r="P196" s="3" t="inlineStr"/>
       <c r="Q196" s="3" t="inlineStr"/>
-      <c r="R196" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
+      <c r="R196" s="3" t="inlineStr"/>
       <c r="S196" s="3" t="inlineStr">
         <is>
-          <t>https://ajuntament.barcelona.cat</t>
+          <t>https://www.discoversevilla.city</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>Primavera Sound Barcelona 2027</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-06-03</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>Parc del Fòrum</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -15339,35 +15299,39 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Scanner bilbao</t>
+          <t>Sónar 2027</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>D8 sorkuntza</t>
+          <t>Sónar de día - Fira Montjuïc</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Bilbao</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="4" t="inlineStr">
         <is>
@@ -15384,17 +15348,135 @@
       </c>
       <c r="N198" s="3" t="inlineStr"/>
       <c r="O198" s="3" t="inlineStr"/>
-      <c r="P198" s="3" t="inlineStr">
+      <c r="P198" s="3" t="inlineStr"/>
+      <c r="Q198" s="3" t="inlineStr"/>
+      <c r="R198" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S198" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>2027-08-15</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Varios Recintos</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr"/>
+      <c r="O199" s="3" t="inlineStr"/>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>Matinée 2000, SLU</t>
+        </is>
+      </c>
+      <c r="Q199" s="3" t="inlineStr"/>
+      <c r="R199" s="3" t="inlineStr"/>
+      <c r="S199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Scanner bilbao</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>D8 sorkuntza</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr"/>
+      <c r="O200" s="3" t="inlineStr"/>
+      <c r="P200" s="3" t="inlineStr">
         <is>
           <t>Copilots Events</t>
         </is>
       </c>
-      <c r="Q198" s="3" t="inlineStr"/>
-      <c r="R198" s="3" t="inlineStr"/>
-      <c r="S198" s="3" t="inlineStr"/>
+      <c r="Q200" s="3" t="inlineStr"/>
+      <c r="R200" s="3" t="inlineStr"/>
+      <c r="S200" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S198"/>
+  <autoFilter ref="A1:S200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15427,7 +15509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/10/2026 13:53</t>
+          <t>19/10/2026 09:45</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15520,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
@@ -15448,7 +15530,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -15535,7 +15617,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -15555,7 +15637,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S200"/>
+  <dimension ref="A1:S201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>603198684</t>
+          <t>629909470</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1038,8 +1038,16 @@
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -2314,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792410179</t>
+          <t>792495001</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2707,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>839683908</t>
+          <t>676068614</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3272,11 +3280,7 @@
           <t>concejalcultura@ayto-torrejon.es</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>800014859</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4021,8 +4025,16 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -4393,7 +4405,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>642255365</t>
+          <t>653177845</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4466,7 +4478,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>761193158</t>
+          <t>686165276</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4540,16 +4552,8 @@
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr"/>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>webmuncipal@ayto-zaragoza.es</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>976721100</t>
-        </is>
-      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr"/>
       <c r="S53" s="3" t="inlineStr">
         <is>
           <t>https://zaragoza.es</t>
@@ -4628,7 +4632,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>839683908</t>
+          <t>676068614</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5752,8 +5756,16 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr"/>
-      <c r="R69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5816,7 +5828,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792410179</t>
+          <t>792495001</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5901,7 +5913,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>640798586</t>
+          <t>664299016</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -6263,16 +6275,8 @@
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="3" t="inlineStr"/>
-      <c r="Q76" s="3" t="inlineStr">
-        <is>
-          <t>webmuncipal@ayto-zaragoza.es</t>
-        </is>
-      </c>
-      <c r="R76" s="3" t="inlineStr">
-        <is>
-          <t>976721100</t>
-        </is>
-      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr"/>
       <c r="S76" s="3" t="inlineStr">
         <is>
           <t>https://zaragoza.es</t>
@@ -7312,7 +7316,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>639263539</t>
+          <t>670408090</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7401,7 +7405,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>633534291</t>
+          <t>873017920</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -7912,7 +7916,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>604909896</t>
+          <t>606989481</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -10980,7 +10984,7 @@
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>603198684</t>
+          <t>629909470</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr">
@@ -11888,7 +11892,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792410165</t>
+          <t>792494990</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12092,8 +12096,16 @@
       <c r="N153" s="3" t="inlineStr"/>
       <c r="O153" s="3" t="inlineStr"/>
       <c r="P153" s="3" t="inlineStr"/>
-      <c r="Q153" s="3" t="inlineStr"/>
-      <c r="R153" s="3" t="inlineStr"/>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-aviles.es</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>653394078</t>
+        </is>
+      </c>
       <c r="S153" s="3" t="inlineStr">
         <is>
           <t>https://aviles.es</t>
@@ -12168,7 +12180,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792402988</t>
+          <t>792487806</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -13027,7 +13039,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>642255365</t>
+          <t>653177845</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13185,7 +13197,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>626900413</t>
+          <t>607290400</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14726,32 +14738,32 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>Nocturna Festival</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t>Sala Upload - Poble Espanyol</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14764,7 +14776,7 @@
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Lion Rock Fest</t>
+          <t>Nocturna Festival</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr"/>
@@ -14777,7 +14789,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+          <t>Sergio Solís Gálvez</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14787,30 +14799,34 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr"/>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
@@ -14819,7 +14835,11 @@
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Lion Rock Fest</t>
+        </is>
+      </c>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
@@ -14830,7 +14850,7 @@
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
         </is>
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
@@ -14840,7 +14860,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -14855,12 +14875,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>SALA EVEN</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
+          <t>Alfajarín</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr"/>
@@ -14883,7 +14903,7 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>SIXTIES SOUND SEVILLA</t>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
         </is>
       </c>
       <c r="Q191" s="3" t="inlineStr"/>
@@ -14893,34 +14913,30 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Roig Arena</t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
+          <t>SEVILLA</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr"/>
       <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
@@ -14929,11 +14945,7 @@
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
-        </is>
-      </c>
+      <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
@@ -14944,7 +14956,7 @@
       <c r="O192" s="3" t="inlineStr"/>
       <c r="P192" s="3" t="inlineStr">
         <is>
-          <t>Live Nation España S.A.U.</t>
+          <t>SIXTIES SOUND SEVILLA</t>
         </is>
       </c>
       <c r="Q192" s="3" t="inlineStr"/>
@@ -14954,7 +14966,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -14969,12 +14981,12 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -14982,16 +14994,8 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>Comunidad Valenciana</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
+      <c r="G193" s="3" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
@@ -15000,146 +15004,146 @@
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr">
-        <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
-        </is>
-      </c>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N193" s="3" t="inlineStr">
-        <is>
-          <t>salamatadero@gmail.com</t>
-        </is>
-      </c>
+      <c r="N193" s="3" t="inlineStr"/>
       <c r="O193" s="3" t="inlineStr"/>
-      <c r="P193" s="3" t="inlineStr"/>
-      <c r="Q193" s="3" t="inlineStr">
-        <is>
-          <t>registro@ayora.es</t>
-        </is>
-      </c>
-      <c r="R193" s="3" t="inlineStr">
-        <is>
-          <t>880898509</t>
-        </is>
-      </c>
-      <c r="S193" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayora.es</t>
-        </is>
-      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>Live Nation España S.A.U.</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="inlineStr"/>
+      <c r="R193" s="3" t="inlineStr"/>
+      <c r="S193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>NoTeMofest acto 4</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Andén 56</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr"/>
+          <t>Ayora</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N194" s="3" t="inlineStr"/>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O194" s="3" t="inlineStr"/>
-      <c r="P194" s="3" t="inlineStr">
-        <is>
-          <t>Steel Souls Producciones</t>
-        </is>
-      </c>
-      <c r="Q194" s="3" t="inlineStr"/>
-      <c r="R194" s="3" t="inlineStr"/>
-      <c r="S194" s="3" t="inlineStr"/>
+      <c r="P194" s="3" t="inlineStr"/>
+      <c r="Q194" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R194" s="3" t="inlineStr">
+        <is>
+          <t>880898509</t>
+        </is>
+      </c>
+      <c r="S194" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>NoTeMofest acto 4</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>Andén 56</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr"/>
+      <c r="G195" s="3" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
@@ -15149,122 +15153,122 @@
       </c>
       <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" s="3" t="inlineStr"/>
-      <c r="P195" s="3" t="inlineStr"/>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>Steel Souls Producciones</t>
+        </is>
+      </c>
       <c r="Q195" s="3" t="inlineStr"/>
-      <c r="R195" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
-      <c r="S195" s="3" t="inlineStr">
-        <is>
-          <t>https://villarrobledo.com</t>
-        </is>
-      </c>
+      <c r="R195" s="3" t="inlineStr"/>
+      <c r="S195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Villarrobledo</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr"/>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N196" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N196" s="3" t="inlineStr"/>
       <c r="O196" s="3" t="inlineStr"/>
       <c r="P196" s="3" t="inlineStr"/>
       <c r="Q196" s="3" t="inlineStr"/>
-      <c r="R196" s="3" t="inlineStr"/>
+      <c r="R196" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
       <c r="S196" s="3" t="inlineStr">
         <is>
-          <t>https://www.discoversevilla.city</t>
+          <t>https://villarrobledo.com</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Interestelar Sevilla 2027</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-05-15</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -15275,46 +15279,50 @@
       </c>
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N197" s="3" t="inlineStr"/>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
       <c r="O197" s="3" t="inlineStr"/>
       <c r="P197" s="3" t="inlineStr"/>
       <c r="Q197" s="3" t="inlineStr"/>
-      <c r="R197" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
+      <c r="R197" s="3" t="inlineStr"/>
       <c r="S197" s="3" t="inlineStr">
         <is>
-          <t>https://ajuntament.barcelona.cat</t>
+          <t>https://www.discoversevilla.city</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>Primavera Sound Barcelona 2027</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-06-03</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>Parc del Fòrum</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -15364,22 +15372,22 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+          <t>Sónar 2027</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Varios Recintos</t>
+          <t>Sónar de día - Fira Montjuïc</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -15392,7 +15400,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr"/>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="4" t="inlineStr">
         <is>
@@ -15400,11 +15412,7 @@
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>Circuit Festival</t>
-        </is>
-      </c>
+      <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
@@ -15413,42 +15421,50 @@
       </c>
       <c r="N199" s="3" t="inlineStr"/>
       <c r="O199" s="3" t="inlineStr"/>
-      <c r="P199" s="3" t="inlineStr">
-        <is>
-          <t>Matinée 2000, SLU</t>
-        </is>
-      </c>
+      <c r="P199" s="3" t="inlineStr"/>
       <c r="Q199" s="3" t="inlineStr"/>
-      <c r="R199" s="3" t="inlineStr"/>
-      <c r="S199" s="3" t="inlineStr"/>
+      <c r="R199" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
+      <c r="S199" s="3" t="inlineStr">
+        <is>
+          <t>https://ajuntament.barcelona.cat</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Scanner bilbao</t>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>D8 sorkuntza</t>
+          <t>Varios Recintos</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="4" t="inlineStr">
@@ -15457,7 +15473,11 @@
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
@@ -15468,15 +15488,68 @@
       <c r="O200" s="3" t="inlineStr"/>
       <c r="P200" s="3" t="inlineStr">
         <is>
-          <t>Copilots Events</t>
+          <t>Matinée 2000, SLU</t>
         </is>
       </c>
       <c r="Q200" s="3" t="inlineStr"/>
       <c r="R200" s="3" t="inlineStr"/>
       <c r="S200" s="3" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Scanner bilbao</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>D8 sorkuntza</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr"/>
+      <c r="O201" s="3" t="inlineStr"/>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>Copilots Events</t>
+        </is>
+      </c>
+      <c r="Q201" s="3" t="inlineStr"/>
+      <c r="R201" s="3" t="inlineStr"/>
+      <c r="S201" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S200"/>
+  <autoFilter ref="A1:S201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15509,7 +15582,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19/10/2026 09:45</t>
+          <t>20/10/2026 09:19</t>
         </is>
       </c>
     </row>
@@ -15520,7 +15593,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -15637,7 +15710,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792495001</t>
+          <t>792581162</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>676068614</t>
+          <t>673667561</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3280,7 +3280,11 @@
           <t>concejalcultura@ayto-torrejon.es</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>763469979</t>
+        </is>
+      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4405,7 +4409,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>653177845</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4632,7 +4636,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>676068614</t>
+          <t>673667561</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>638914436</t>
+          <t>639190941</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -5828,7 +5832,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792495001</t>
+          <t>792581162</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5913,7 +5917,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>664299016</t>
+          <t>618312035</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7316,7 +7320,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>670408090</t>
+          <t>625292825</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7405,7 +7409,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>873017920</t>
+          <t>740334154</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -7916,7 +7920,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>606989481</t>
+          <t>601795196</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -7994,11 +7998,7 @@
           <t>Nyoman Producciones Honestas S.L</t>
         </is>
       </c>
-      <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>fiestas@ayto-salobrena.org</t>
-        </is>
-      </c>
+      <c r="Q99" s="3" t="inlineStr"/>
       <c r="R99" s="3" t="inlineStr">
         <is>
           <t>654639979</t>
@@ -8906,16 +8906,8 @@
           <t>NECESIDAD DE FACILITAR DATOS PERSONALES. L</t>
         </is>
       </c>
-      <c r="Q111" s="3" t="inlineStr">
-        <is>
-          <t>delegaciondecultura@marbella.es</t>
-        </is>
-      </c>
-      <c r="R111" s="3" t="inlineStr">
-        <is>
-          <t>621368620</t>
-        </is>
-      </c>
+      <c r="Q111" s="3" t="inlineStr"/>
+      <c r="R111" s="3" t="inlineStr"/>
       <c r="S111" s="3" t="inlineStr">
         <is>
           <t>https://ayuntamiento.marbella.es</t>
@@ -10896,16 +10888,8 @@
       </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr"/>
-      <c r="Q137" s="3" t="inlineStr">
-        <is>
-          <t>delegaciondecultura@marbella.es</t>
-        </is>
-      </c>
-      <c r="R137" s="3" t="inlineStr">
-        <is>
-          <t>621368620</t>
-        </is>
-      </c>
+      <c r="Q137" s="3" t="inlineStr"/>
+      <c r="R137" s="3" t="inlineStr"/>
       <c r="S137" s="3" t="inlineStr">
         <is>
           <t>https://ayuntamiento.marbella.es</t>
@@ -11892,7 +11876,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792494990</t>
+          <t>792581143</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12180,7 +12164,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792487806</t>
+          <t>792573970</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12558,16 +12542,8 @@
       <c r="N159" s="3" t="inlineStr"/>
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="3" t="inlineStr"/>
-      <c r="Q159" s="3" t="inlineStr">
-        <is>
-          <t>cultura.escuelasmunicipales@aytoguadalajara.es</t>
-        </is>
-      </c>
-      <c r="R159" s="3" t="inlineStr">
-        <is>
-          <t>949887070</t>
-        </is>
-      </c>
+      <c r="Q159" s="3" t="inlineStr"/>
+      <c r="R159" s="3" t="inlineStr"/>
       <c r="S159" s="3" t="inlineStr">
         <is>
           <t>https://www.guadalajara.es</t>
@@ -13039,7 +13015,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>653177845</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13197,7 +13173,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>607290400</t>
+          <t>626900413</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -15582,7 +15558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/10/2026 09:19</t>
+          <t>21/10/2026 09:15</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>880898509</t>
+          <t>648418329</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792581162</t>
+          <t>792667719</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>673667561</t>
+          <t>736673607</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -2951,16 +2951,8 @@
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-caceres.es</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>618380445</t>
-        </is>
-      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
       <c r="S32" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-caceres.es</t>
@@ -3280,11 +3272,7 @@
           <t>concejalcultura@ayto-torrejon.es</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>763469979</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4409,7 +4397,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>633681427</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4482,7 +4470,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>686165276</t>
+          <t>657226584</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4556,8 +4544,16 @@
       <c r="N53" s="3" t="inlineStr"/>
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr"/>
-      <c r="Q53" s="3" t="inlineStr"/>
-      <c r="R53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>webmuncipal@ayto-zaragoza.es</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>976721100</t>
+        </is>
+      </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
           <t>https://zaragoza.es</t>
@@ -4636,7 +4632,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>673667561</t>
+          <t>736673607</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5832,7 +5828,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792581162</t>
+          <t>792667719</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5917,7 +5913,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>618312035</t>
+          <t>664299016</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -6279,8 +6275,16 @@
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="3" t="inlineStr"/>
-      <c r="Q76" s="3" t="inlineStr"/>
-      <c r="R76" s="3" t="inlineStr"/>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>webmuncipal@ayto-zaragoza.es</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>976721100</t>
+        </is>
+      </c>
       <c r="S76" s="3" t="inlineStr">
         <is>
           <t>https://zaragoza.es</t>
@@ -7320,7 +7324,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>625292825</t>
+          <t>646467487</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7409,7 +7413,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>740334154</t>
+          <t>715215006</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -7920,7 +7924,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>601795196</t>
+          <t>606989481</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -8140,16 +8144,8 @@
       <c r="N101" s="3" t="inlineStr"/>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="3" t="inlineStr"/>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>canet.alcaldia@canetdemar.cat</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>937943940</t>
-        </is>
-      </c>
+      <c r="Q101" s="3" t="inlineStr"/>
+      <c r="R101" s="3" t="inlineStr"/>
       <c r="S101" s="3" t="inlineStr">
         <is>
           <t>https://www.canetdemar.cat</t>
@@ -8678,7 +8674,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>733346966</t>
+          <t>792660521</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -8906,8 +8902,16 @@
           <t>NECESIDAD DE FACILITAR DATOS PERSONALES. L</t>
         </is>
       </c>
-      <c r="Q111" s="3" t="inlineStr"/>
-      <c r="R111" s="3" t="inlineStr"/>
+      <c r="Q111" s="3" t="inlineStr">
+        <is>
+          <t>delegaciondecultura@marbella.es</t>
+        </is>
+      </c>
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>621368620</t>
+        </is>
+      </c>
       <c r="S111" s="3" t="inlineStr">
         <is>
           <t>https://ayuntamiento.marbella.es</t>
@@ -9721,11 +9725,7 @@
       </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="3" t="inlineStr"/>
-      <c r="Q122" s="3" t="inlineStr">
-        <is>
-          <t>adminportal@ayto-santander.es</t>
-        </is>
-      </c>
+      <c r="Q122" s="3" t="inlineStr"/>
       <c r="R122" s="3" t="inlineStr"/>
       <c r="S122" s="3" t="inlineStr">
         <is>
@@ -10888,8 +10888,16 @@
       </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr"/>
-      <c r="Q137" s="3" t="inlineStr"/>
-      <c r="R137" s="3" t="inlineStr"/>
+      <c r="Q137" s="3" t="inlineStr">
+        <is>
+          <t>delegaciondecultura@marbella.es</t>
+        </is>
+      </c>
+      <c r="R137" s="3" t="inlineStr">
+        <is>
+          <t>621368620</t>
+        </is>
+      </c>
       <c r="S137" s="3" t="inlineStr">
         <is>
           <t>https://ayuntamiento.marbella.es</t>
@@ -11876,7 +11884,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792581143</t>
+          <t>792667707</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12164,7 +12172,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792573970</t>
+          <t>792660525</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12542,8 +12550,16 @@
       <c r="N159" s="3" t="inlineStr"/>
       <c r="O159" s="3" t="inlineStr"/>
       <c r="P159" s="3" t="inlineStr"/>
-      <c r="Q159" s="3" t="inlineStr"/>
-      <c r="R159" s="3" t="inlineStr"/>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>cultura.escuelasmunicipales@aytoguadalajara.es</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="inlineStr">
+        <is>
+          <t>949887070</t>
+        </is>
+      </c>
       <c r="S159" s="3" t="inlineStr">
         <is>
           <t>https://www.guadalajara.es</t>
@@ -13015,7 +13031,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>633681427</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13173,7 +13189,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>626900413</t>
+          <t>623262727</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14553,16 +14569,8 @@
           <t>En Mediaprogramas S.L</t>
         </is>
       </c>
-      <c r="Q186" s="3" t="inlineStr">
-        <is>
-          <t>informacion@ayto-caceres.es</t>
-        </is>
-      </c>
-      <c r="R186" s="3" t="inlineStr">
-        <is>
-          <t>618380445</t>
-        </is>
-      </c>
+      <c r="Q186" s="3" t="inlineStr"/>
+      <c r="R186" s="3" t="inlineStr"/>
       <c r="S186" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-caceres.es</t>
@@ -15076,7 +15084,7 @@
       </c>
       <c r="R194" s="3" t="inlineStr">
         <is>
-          <t>880898509</t>
+          <t>648418329</t>
         </is>
       </c>
       <c r="S194" s="3" t="inlineStr">
@@ -15558,7 +15566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21/10/2026 09:15</t>
+          <t>22/10/2026 09:18</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1038,16 +1038,8 @@
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -2322,7 +2314,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792667719</t>
+          <t>792753902</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2707,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>736673607</t>
+          <t>734202368</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -2870,16 +2862,8 @@
       </c>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t>atencionciudadana@fuengirola.org</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>629152084</t>
-        </is>
-      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
       <c r="S31" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -2951,8 +2935,16 @@
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-caceres.es</t>
@@ -4017,16 +4009,8 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -4301,16 +4285,8 @@
           <t>THE FULANITA SISTERS S.L</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>atencionciudadana@fuengirola.org</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>629152084</t>
-        </is>
-      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
       <c r="S50" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -4397,7 +4373,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>633681427</t>
+          <t>612380061</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4470,7 +4446,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>657226584</t>
+          <t>686165276</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4632,7 +4608,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>736673607</t>
+          <t>734202368</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5756,16 +5732,8 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr"/>
       <c r="S69" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5828,7 +5796,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792667719</t>
+          <t>792753902</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7324,7 +7292,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>646467487</t>
+          <t>637865246</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7413,7 +7381,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>715215006</t>
+          <t>873017920</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -8144,8 +8112,16 @@
       <c r="N101" s="3" t="inlineStr"/>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="3" t="inlineStr"/>
-      <c r="Q101" s="3" t="inlineStr"/>
-      <c r="R101" s="3" t="inlineStr"/>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>canet.alcaldia@canetdemar.cat</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>937943940</t>
+        </is>
+      </c>
       <c r="S101" s="3" t="inlineStr">
         <is>
           <t>https://www.canetdemar.cat</t>
@@ -8674,7 +8650,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>792660521</t>
+          <t>733346966</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -9725,7 +9701,11 @@
       </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="3" t="inlineStr"/>
-      <c r="Q122" s="3" t="inlineStr"/>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>adminportal@ayto-santander.es</t>
+        </is>
+      </c>
       <c r="R122" s="3" t="inlineStr"/>
       <c r="S122" s="3" t="inlineStr">
         <is>
@@ -11884,7 +11864,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792667707</t>
+          <t>792753894</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12172,7 +12152,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792660525</t>
+          <t>792746708</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12635,16 +12615,8 @@
       </c>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="3" t="inlineStr"/>
-      <c r="Q160" s="3" t="inlineStr">
-        <is>
-          <t>atencionciudadana@fuengirola.org</t>
-        </is>
-      </c>
-      <c r="R160" s="3" t="inlineStr">
-        <is>
-          <t>629152084</t>
-        </is>
-      </c>
+      <c r="Q160" s="3" t="inlineStr"/>
+      <c r="R160" s="3" t="inlineStr"/>
       <c r="S160" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -13031,7 +13003,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>633681427</t>
+          <t>612380061</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13189,7 +13161,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>623262727</t>
+          <t>626900413</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14434,211 +14406,247 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Festa Presentació Vida Festival 2027: La Publicitat &amp; Bernal</t>
+          <t>Horteralia Cáceres 2026</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Antiga Fàbrica Estrella Damm</t>
+          <t>Recinto Ferial de Cáceres</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cáceres</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr"/>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>Extremadura</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Pop</t>
+        </is>
+      </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>CANO, CUPIDO, CYRIL KAMER</t>
+        </is>
+      </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Vida Records &amp; Friends, Vida Festival</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="inlineStr"/>
+          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
+        </is>
+      </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N185" s="3" t="inlineStr"/>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>dpo@mediaprogramas.com</t>
+        </is>
+      </c>
       <c r="O185" s="3" t="inlineStr"/>
       <c r="P185" s="3" t="inlineStr">
         <is>
-          <t>Sitback Produccions, S.L.</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr"/>
-      <c r="R185" s="3" t="inlineStr"/>
-      <c r="S185" s="3" t="inlineStr"/>
+          <t>En Mediaprogramas S.L</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr">
+        <is>
+          <t>informacion@ayto-caceres.es</t>
+        </is>
+      </c>
+      <c r="R185" s="3" t="inlineStr">
+        <is>
+          <t>618380445</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayto-caceres.es</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Horteralia Cáceres 2026</t>
+          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Cáceres</t>
+          <t xml:space="preserve">Pub La chica de ayer </t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Cáceres</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="inlineStr">
-        <is>
-          <t>Cáceres</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr"/>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>CANO, CUPIDO, CYRIL KAMER</t>
-        </is>
-      </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Camela, Ladilla rusa, Amatria, Cherri Coke, El Gato con Jotas, Los Desgraciaus, Los Inhumanos, Nebulossa, Sharonne</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mevoyacaceres.com/festival-horteralia-de-caceres/</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr">
-        <is>
-          <t>dpo@mediaprogramas.com</t>
-        </is>
-      </c>
+      <c r="N186" s="3" t="inlineStr"/>
       <c r="O186" s="3" t="inlineStr"/>
       <c r="P186" s="3" t="inlineStr">
         <is>
-          <t>En Mediaprogramas S.L</t>
+          <t>La chica Fest</t>
         </is>
       </c>
       <c r="Q186" s="3" t="inlineStr"/>
       <c r="R186" s="3" t="inlineStr"/>
-      <c r="S186" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayto-caceres.es</t>
-        </is>
-      </c>
+      <c r="S186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pub La chica de ayer </t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="inlineStr"/>
-      <c r="G187" s="3" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
+          <t>Chantada</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr"/>
-      <c r="K187" s="2" t="inlineStr"/>
-      <c r="L187" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr"/>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr">
-        <is>
-          <t>La chica Fest</t>
-        </is>
-      </c>
-      <c r="Q187" s="3" t="inlineStr"/>
-      <c r="R187" s="3" t="inlineStr"/>
-      <c r="S187" s="3" t="inlineStr"/>
+      <c r="P187" s="3" t="inlineStr"/>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S187" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>Nocturna Festival</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -14648,106 +14656,78 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Sala Upload - Poble Espanyol</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>Nocturna Festival</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N188" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N188" s="3" t="inlineStr"/>
       <c r="O188" s="3" t="inlineStr"/>
-      <c r="P188" s="3" t="inlineStr"/>
-      <c r="Q188" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R188" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S188" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>Sergio Solís Gálvez</t>
+        </is>
+      </c>
+      <c r="Q188" s="3" t="inlineStr"/>
+      <c r="R188" s="3" t="inlineStr"/>
+      <c r="S188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sala Upload - Poble Espanyol</t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr"/>
@@ -14760,7 +14740,7 @@
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
+          <t>Lion Rock Fest</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr"/>
@@ -14773,7 +14753,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>Sergio Solís Gálvez</t>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14783,34 +14763,30 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
+          <t>Alfajarín</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr"/>
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="4" t="inlineStr">
@@ -14819,11 +14795,7 @@
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Lion Rock Fest</t>
-        </is>
-      </c>
+      <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
@@ -14834,7 +14806,7 @@
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr">
         <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
         </is>
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
@@ -14844,7 +14816,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -14859,12 +14831,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
+          <t>SEVILLA</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr"/>
@@ -14887,7 +14859,7 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+          <t>SIXTIES SOUND SEVILLA</t>
         </is>
       </c>
       <c r="Q191" s="3" t="inlineStr"/>
@@ -14897,30 +14869,34 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
+          <t>Festa Presentació Vida Festival 2027: Cervatana</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>SALA EVEN</t>
+          <t>Antiga Fàbrica Estrella Damm</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="G192" s="3" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="4" t="inlineStr">
@@ -14929,7 +14905,11 @@
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Vida Records &amp; Friends, Vida Festival</t>
+        </is>
+      </c>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
@@ -14940,7 +14920,7 @@
       <c r="O192" s="3" t="inlineStr"/>
       <c r="P192" s="3" t="inlineStr">
         <is>
-          <t>SIXTIES SOUND SEVILLA</t>
+          <t>Sitback Produccions, S.L.</t>
         </is>
       </c>
       <c r="Q192" s="3" t="inlineStr"/>
@@ -15566,7 +15546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22/10/2026 09:18</t>
+          <t>23/10/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -15694,7 +15674,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -15704,7 +15684,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1038,8 +1038,16 @@
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -1126,7 +1134,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>648418329</t>
+          <t>616472692</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -2314,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792753902</t>
+          <t>792838669</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2707,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>734202368</t>
+          <t>655414209</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -2862,8 +2870,16 @@
       </c>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -3259,12 +3275,12 @@
           <t>ELROW GLOBAL S.L</t>
         </is>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>concejalcultura@ayto-torrejon.es</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>775893321</t>
+        </is>
+      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4009,8 +4025,16 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -4285,8 +4309,16 @@
           <t>THE FULANITA SISTERS S.L</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr"/>
-      <c r="R50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -4373,7 +4405,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>612380061</t>
+          <t>712695907</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4446,7 +4478,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>686165276</t>
+          <t>671257261</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4608,7 +4640,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>734202368</t>
+          <t>655414209</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5732,8 +5764,16 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr"/>
-      <c r="R69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5796,7 +5836,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792753902</t>
+          <t>792838669</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7292,7 +7332,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>637865246</t>
+          <t>646467487</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8650,7 +8690,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>733346966</t>
+          <t>792831471</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -11864,7 +11904,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792753894</t>
+          <t>792838655</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12152,7 +12192,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792746708</t>
+          <t>792831476</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12615,8 +12655,16 @@
       </c>
       <c r="O160" s="3" t="inlineStr"/>
       <c r="P160" s="3" t="inlineStr"/>
-      <c r="Q160" s="3" t="inlineStr"/>
-      <c r="R160" s="3" t="inlineStr"/>
+      <c r="Q160" s="3" t="inlineStr">
+        <is>
+          <t>atencionciudadana@fuengirola.org</t>
+        </is>
+      </c>
+      <c r="R160" s="3" t="inlineStr">
+        <is>
+          <t>629152084</t>
+        </is>
+      </c>
       <c r="S160" s="3" t="inlineStr">
         <is>
           <t>https://www.fuengirola.es</t>
@@ -13003,7 +13051,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>612380061</t>
+          <t>712695907</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13226,11 +13274,7 @@
       </c>
       <c r="N168" s="3" t="inlineStr"/>
       <c r="O168" s="3" t="inlineStr"/>
-      <c r="P168" s="3" t="inlineStr">
-        <is>
-          <t>Debeat Swing</t>
-        </is>
-      </c>
+      <c r="P168" s="3" t="inlineStr"/>
       <c r="Q168" s="3" t="inlineStr"/>
       <c r="R168" s="3" t="inlineStr"/>
       <c r="S168" s="3" t="inlineStr"/>
@@ -14466,7 +14510,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>confirmado</t>
+          <t>por confirmar</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -15064,7 +15108,7 @@
       </c>
       <c r="R194" s="3" t="inlineStr">
         <is>
-          <t>648418329</t>
+          <t>616472692</t>
         </is>
       </c>
       <c r="S194" s="3" t="inlineStr">
@@ -15546,7 +15590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23/10/2026 09:13</t>
+          <t>24/10/2026 08:47</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1038,16 +1038,8 @@
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -2322,7 +2314,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792838669</t>
+          <t>792922453</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2707,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>655414209</t>
+          <t>605111259</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3276,11 +3268,7 @@
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>775893321</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4025,16 +4013,8 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -4405,7 +4385,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>712695907</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4478,7 +4458,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>671257261</t>
+          <t>686165276</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4640,7 +4620,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>655414209</t>
+          <t>605111259</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5764,16 +5744,8 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>alcaldia@benidorm.org</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>639341771</t>
-        </is>
-      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr"/>
       <c r="S69" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5836,7 +5808,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792838669</t>
+          <t>792922453</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7332,7 +7304,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>646467487</t>
+          <t>619061519</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8690,7 +8662,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>792831471</t>
+          <t>733346966</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -9665,11 +9637,7 @@
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr"/>
       <c r="Q121" s="3" t="inlineStr"/>
-      <c r="R121" s="3" t="inlineStr">
-        <is>
-          <t>879866197</t>
-        </is>
-      </c>
+      <c r="R121" s="3" t="inlineStr"/>
       <c r="S121" s="3" t="inlineStr">
         <is>
           <t>https://www.castellonexiste.es</t>
@@ -10539,16 +10507,8 @@
       </c>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="3" t="inlineStr"/>
-      <c r="Q132" s="3" t="inlineStr">
-        <is>
-          <t>admon@aldeacentenera.es</t>
-        </is>
-      </c>
-      <c r="R132" s="3" t="inlineStr">
-        <is>
-          <t>723100746</t>
-        </is>
-      </c>
+      <c r="Q132" s="3" t="inlineStr"/>
+      <c r="R132" s="3" t="inlineStr"/>
       <c r="S132" s="3" t="inlineStr">
         <is>
           <t>https://www.aldeacentenera.es</t>
@@ -10692,11 +10652,7 @@
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr"/>
-      <c r="P134" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLUB MUTANTE </t>
-        </is>
-      </c>
+      <c r="P134" s="3" t="inlineStr"/>
       <c r="Q134" s="3" t="inlineStr"/>
       <c r="R134" s="3" t="inlineStr"/>
       <c r="S134" s="3" t="inlineStr">
@@ -11904,7 +11860,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792838655</t>
+          <t>792922442</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12192,7 +12148,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>792831476</t>
+          <t>757168264</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -13051,7 +13007,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>712695907</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -15590,7 +15546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24/10/2026 08:47</t>
+          <t>25/10/2026 09:03</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S201"/>
+  <dimension ref="A1:S200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1038,8 +1038,16 @@
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -2314,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>792922453</t>
+          <t>793012677</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -4013,8 +4021,16 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5744,8 +5760,16 @@
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="inlineStr"/>
-      <c r="R69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>alcaldia@benidorm.org</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>639341771</t>
+        </is>
+      </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
           <t>https://www.ayuntamiento.org</t>
@@ -5808,7 +5832,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>792922453</t>
+          <t>793012677</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7304,7 +7328,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>619061519</t>
+          <t>605649564</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8662,7 +8686,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>733346966</t>
+          <t>669616556</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -9637,7 +9661,11 @@
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr"/>
       <c r="Q121" s="3" t="inlineStr"/>
-      <c r="R121" s="3" t="inlineStr"/>
+      <c r="R121" s="3" t="inlineStr">
+        <is>
+          <t>879866197</t>
+        </is>
+      </c>
       <c r="S121" s="3" t="inlineStr">
         <is>
           <t>https://www.castellonexiste.es</t>
@@ -11860,7 +11888,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>792922442</t>
+          <t>793012662</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12148,7 +12176,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>757168264</t>
+          <t>793009085</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -14499,65 +14527,101 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>La CHICA FEST. Actuación de Elegante embustero. Formato trío</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pub La chica de ayer </t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="inlineStr"/>
-      <c r="G186" s="3" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr"/>
+          <t>Chantada</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O186" s="3" t="inlineStr"/>
-      <c r="P186" s="3" t="inlineStr">
-        <is>
-          <t>La chica Fest</t>
-        </is>
-      </c>
-      <c r="Q186" s="3" t="inlineStr"/>
-      <c r="R186" s="3" t="inlineStr"/>
-      <c r="S186" s="3" t="inlineStr"/>
+      <c r="P186" s="3" t="inlineStr"/>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>Nocturna Festival</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -14567,106 +14631,78 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Sala Upload - Poble Espanyol</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>Nocturna Festival</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N187" s="3" t="inlineStr"/>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R187" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S187" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>Sergio Solís Gálvez</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr"/>
+      <c r="S187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
+          <t>GALILEO ROCK FEST</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Sala Upload - Poble Espanyol</t>
+          <t>Sala Galileo Galilei</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr"/>
@@ -14679,7 +14715,7 @@
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
+          <t>Lion Rock Fest</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr"/>
@@ -14692,7 +14728,7 @@
       <c r="O188" s="3" t="inlineStr"/>
       <c r="P188" s="3" t="inlineStr">
         <is>
-          <t>Sergio Solís Gálvez</t>
+          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
         </is>
       </c>
       <c r="Q188" s="3" t="inlineStr"/>
@@ -14702,34 +14738,30 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GALILEO ROCK FEST</t>
+          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Sala Galileo Galilei</t>
+          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
+          <t>Alfajarín</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr"/>
       <c r="G189" s="3" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" s="4" t="inlineStr">
@@ -14738,11 +14770,7 @@
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>Lion Rock Fest</t>
-        </is>
-      </c>
+      <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
@@ -14753,7 +14781,7 @@
       <c r="O189" s="3" t="inlineStr"/>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>Artisti-K Prod. Mus. y Cult, S.L.</t>
+          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
         </is>
       </c>
       <c r="Q189" s="3" t="inlineStr"/>
@@ -14763,7 +14791,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ALFAJARÍN, CULTURA ELECTRÓNICA 2026 (The Raven Clan)</t>
+          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -14778,12 +14806,12 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALÓN CULTURAL “LA PORTAZA” </t>
+          <t>SALA EVEN</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Alfajarín</t>
+          <t>SEVILLA</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr"/>
@@ -14806,7 +14834,7 @@
       <c r="O190" s="3" t="inlineStr"/>
       <c r="P190" s="3" t="inlineStr">
         <is>
-          <t>AYUNTAMIENTO DE ALFAJARÍN</t>
+          <t>SIXTIES SOUND SEVILLA</t>
         </is>
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
@@ -14816,30 +14844,34 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>IV FESTIVAL SEVILLA SIXTIES SOUND</t>
+          <t>Festa Presentació Vida Festival 2027: Cervatana</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>SALA EVEN</t>
+          <t>Antiga Fàbrica Estrella Damm</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>SEVILLA</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="4" t="inlineStr">
@@ -14848,7 +14880,11 @@
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
-      <c r="K191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>Vida Records &amp; Friends, Vida Festival</t>
+        </is>
+      </c>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
@@ -14859,7 +14895,7 @@
       <c r="O191" s="3" t="inlineStr"/>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>SIXTIES SOUND SEVILLA</t>
+          <t>Sitback Produccions, S.L.</t>
         </is>
       </c>
       <c r="Q191" s="3" t="inlineStr"/>
@@ -14869,32 +14905,32 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Festa Presentació Vida Festival 2027: Cervatana</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Antiga Fàbrica Estrella Damm</t>
+          <t>Roig Arena</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr"/>
@@ -14907,7 +14943,7 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Vida Records &amp; Friends, Vida Festival</t>
+          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr"/>
@@ -14920,7 +14956,7 @@
       <c r="O192" s="3" t="inlineStr"/>
       <c r="P192" s="3" t="inlineStr">
         <is>
-          <t>Sitback Produccions, S.L.</t>
+          <t>Live Nation España S.A.U.</t>
         </is>
       </c>
       <c r="Q192" s="3" t="inlineStr"/>
@@ -14930,7 +14966,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA - CONCIERTO ESTOPA</t>
+          <t>Metal Bee 2026</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -14945,21 +14981,29 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Roig Arena</t>
+          <t>Sala Matadero</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
+          <t>Ayora</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr"/>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
@@ -14968,146 +15012,146 @@
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>IBERDROLA MUSIC FESTIVAL VALENCIA, Estopa</t>
-        </is>
-      </c>
-      <c r="L193" s="2" t="inlineStr"/>
+          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
+        </is>
+      </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N193" s="3" t="inlineStr"/>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>salamatadero@gmail.com</t>
+        </is>
+      </c>
       <c r="O193" s="3" t="inlineStr"/>
-      <c r="P193" s="3" t="inlineStr">
-        <is>
-          <t>Live Nation España S.A.U.</t>
-        </is>
-      </c>
-      <c r="Q193" s="3" t="inlineStr"/>
-      <c r="R193" s="3" t="inlineStr"/>
-      <c r="S193" s="3" t="inlineStr"/>
+      <c r="P193" s="3" t="inlineStr"/>
+      <c r="Q193" s="3" t="inlineStr">
+        <is>
+          <t>registro@ayora.es</t>
+        </is>
+      </c>
+      <c r="R193" s="3" t="inlineStr">
+        <is>
+          <t>616472692</t>
+        </is>
+      </c>
+      <c r="S193" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayora.es</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Metal Bee 2026</t>
+          <t>NoTeMofest acto 4</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Sala Matadero</t>
+          <t>Andén 56</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Ayora</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>Comunidad Valenciana</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr"/>
+      <c r="G194" s="3" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="4" t="inlineStr">
         <is>
           <t>bajo</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Leo Jiménez, Débler Eternia, Salduie, Seventh Hell, Six Burning Knives</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="inlineStr">
-        <is>
-          <t>http://tickets.salamatadero.com/es/matadero-live-music/iv-festival-metalbee/2026-11-28/</t>
-        </is>
-      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N194" s="3" t="inlineStr">
-        <is>
-          <t>salamatadero@gmail.com</t>
-        </is>
-      </c>
+      <c r="N194" s="3" t="inlineStr"/>
       <c r="O194" s="3" t="inlineStr"/>
-      <c r="P194" s="3" t="inlineStr"/>
-      <c r="Q194" s="3" t="inlineStr">
-        <is>
-          <t>registro@ayora.es</t>
-        </is>
-      </c>
-      <c r="R194" s="3" t="inlineStr">
-        <is>
-          <t>616472692</t>
-        </is>
-      </c>
-      <c r="S194" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ayora.es</t>
-        </is>
-      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>Steel Souls Producciones</t>
+        </is>
+      </c>
+      <c r="Q194" s="3" t="inlineStr"/>
+      <c r="R194" s="3" t="inlineStr"/>
+      <c r="S194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>NoTeMofest acto 4</t>
+          <t>Viña Rock 2027</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-05-01</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Andén 56</t>
+          <t>Recinto Ferial de Villarrobledo</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr"/>
-      <c r="G195" s="3" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr"/>
+          <t>Villarrobledo</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="inlineStr"/>
+          <t>medio</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO</t>
+        </is>
+      </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
@@ -15117,122 +15161,122 @@
       </c>
       <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" s="3" t="inlineStr"/>
-      <c r="P195" s="3" t="inlineStr">
-        <is>
-          <t>Steel Souls Producciones</t>
-        </is>
-      </c>
+      <c r="P195" s="3" t="inlineStr"/>
       <c r="Q195" s="3" t="inlineStr"/>
-      <c r="R195" s="3" t="inlineStr"/>
-      <c r="S195" s="3" t="inlineStr"/>
+      <c r="R195" s="3" t="inlineStr">
+        <is>
+          <t>736908127</t>
+        </is>
+      </c>
+      <c r="S195" s="3" t="inlineStr">
+        <is>
+          <t>https://villarrobledo.com</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Viña Rock 2027</t>
+          <t>Interestelar Sevilla 2027</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>2027-04-29</t>
+          <t>2027-05-14</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>2027-05-01</t>
+          <t>2027-05-15</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Recinto Ferial de Villarrobledo</t>
+          <t>Centro Andaluz de Arte Contemporáneo</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Villarrobledo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Castilla-La Mancha</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t>medio</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
+        </is>
+      </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N196" s="3" t="inlineStr"/>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>hola@conciertosensevilla.es</t>
+        </is>
+      </c>
       <c r="O196" s="3" t="inlineStr"/>
       <c r="P196" s="3" t="inlineStr"/>
       <c r="Q196" s="3" t="inlineStr"/>
-      <c r="R196" s="3" t="inlineStr">
-        <is>
-          <t>736908127</t>
-        </is>
-      </c>
+      <c r="R196" s="3" t="inlineStr"/>
       <c r="S196" s="3" t="inlineStr">
         <is>
-          <t>https://villarrobledo.com</t>
+          <t>https://www.discoversevilla.city</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Interestelar Sevilla 2027</t>
+          <t>Primavera Sound Barcelona 2027</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>2027-05-14</t>
+          <t>2027-06-03</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Centro Andaluz de Arte Contemporáneo</t>
+          <t>Parc del Fòrum</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -15243,50 +15287,46 @@
       </c>
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
-      <c r="L197" s="2" t="inlineStr">
-        <is>
-          <t>https://conciertosensevilla.es/interestelar-sevilla-2027-viva-suecia-y-la-oreja-de-van-gogh-primeros-nombres-del-cartel/</t>
-        </is>
-      </c>
+      <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N197" s="3" t="inlineStr">
-        <is>
-          <t>hola@conciertosensevilla.es</t>
-        </is>
-      </c>
+      <c r="N197" s="3" t="inlineStr"/>
       <c r="O197" s="3" t="inlineStr"/>
       <c r="P197" s="3" t="inlineStr"/>
       <c r="Q197" s="3" t="inlineStr"/>
-      <c r="R197" s="3" t="inlineStr"/>
+      <c r="R197" s="3" t="inlineStr">
+        <is>
+          <t>616401389</t>
+        </is>
+      </c>
       <c r="S197" s="3" t="inlineStr">
         <is>
-          <t>https://www.discoversevilla.city</t>
+          <t>https://ajuntament.barcelona.cat</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Primavera Sound Barcelona 2027</t>
+          <t>Sónar 2027</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-03</t>
+          <t>2027-06-17</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2027-06-19</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Parc del Fòrum</t>
+          <t>Sónar de día - Fira Montjuïc</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -15336,22 +15376,22 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Sónar 2027</t>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>2027-06-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2027-06-19</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Sónar de día - Fira Montjuïc</t>
+          <t>Varios Recintos</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -15364,11 +15404,7 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
+      <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="4" t="inlineStr">
         <is>
@@ -15376,7 +15412,11 @@
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
@@ -15385,50 +15425,42 @@
       </c>
       <c r="N199" s="3" t="inlineStr"/>
       <c r="O199" s="3" t="inlineStr"/>
-      <c r="P199" s="3" t="inlineStr"/>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>Matinée 2000, SLU</t>
+        </is>
+      </c>
       <c r="Q199" s="3" t="inlineStr"/>
-      <c r="R199" s="3" t="inlineStr">
-        <is>
-          <t>616401389</t>
-        </is>
-      </c>
-      <c r="S199" s="3" t="inlineStr">
-        <is>
-          <t>https://ajuntament.barcelona.cat</t>
-        </is>
-      </c>
+      <c r="R199" s="3" t="inlineStr"/>
+      <c r="S199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+          <t>Scanner bilbao</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-09-17</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Varios Recintos</t>
+          <t>D8 sorkuntza</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr"/>
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="4" t="inlineStr">
@@ -15437,11 +15469,7 @@
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>Circuit Festival</t>
-        </is>
-      </c>
+      <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
@@ -15452,68 +15480,15 @@
       <c r="O200" s="3" t="inlineStr"/>
       <c r="P200" s="3" t="inlineStr">
         <is>
-          <t>Matinée 2000, SLU</t>
+          <t>Copilots Events</t>
         </is>
       </c>
       <c r="Q200" s="3" t="inlineStr"/>
       <c r="R200" s="3" t="inlineStr"/>
       <c r="S200" s="3" t="inlineStr"/>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Scanner bilbao</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>2027-09-17</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>D8 sorkuntza</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr"/>
-      <c r="G201" s="3" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr"/>
-      <c r="I201" s="4" t="inlineStr">
-        <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="inlineStr">
-        <is>
-          <t>confirmado</t>
-        </is>
-      </c>
-      <c r="N201" s="3" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr"/>
-      <c r="P201" s="3" t="inlineStr">
-        <is>
-          <t>Copilots Events</t>
-        </is>
-      </c>
-      <c r="Q201" s="3" t="inlineStr"/>
-      <c r="R201" s="3" t="inlineStr"/>
-      <c r="S201" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S201"/>
+  <autoFilter ref="A1:S200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15546,7 +15521,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25/10/2026 09:03</t>
+          <t>26/10/2026 10:07</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15532,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
@@ -15674,7 +15649,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>793012677</t>
+          <t>793097667</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>605111259</t>
+          <t>654451445</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3276,7 +3276,11 @@
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>726643362</t>
+        </is>
+      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4401,7 +4405,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>641490590</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4636,7 +4640,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>605111259</t>
+          <t>654451445</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5832,7 +5836,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>793012677</t>
+          <t>793097667</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5917,7 +5921,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>664299016</t>
+          <t>620070669</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7328,7 +7332,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>605649564</t>
+          <t>646467487</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8686,7 +8690,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>669616556</t>
+          <t>733346966</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -10535,8 +10539,16 @@
       </c>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="3" t="inlineStr"/>
-      <c r="Q132" s="3" t="inlineStr"/>
-      <c r="R132" s="3" t="inlineStr"/>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>admon@aldeacentenera.es</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="inlineStr">
+        <is>
+          <t>723100812</t>
+        </is>
+      </c>
       <c r="S132" s="3" t="inlineStr">
         <is>
           <t>https://www.aldeacentenera.es</t>
@@ -11888,7 +11900,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>793012662</t>
+          <t>793097655</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12176,7 +12188,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>793009085</t>
+          <t>793094074</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -13035,7 +13047,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>641490590</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -15521,7 +15533,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26/10/2026 10:07</t>
+          <t>27/10/2026 09:43</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>616472692</t>
+          <t>880898509</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>793097667</t>
+          <t>793186775</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>654451445</t>
+          <t>644550455</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="Q36" s="3" t="inlineStr"/>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>726643362</t>
+          <t>830184285</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>641490590</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>686165276</t>
+          <t>628006791</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>654451445</t>
+          <t>644550455</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5836,7 +5836,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>793097667</t>
+          <t>793186775</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>620070669</t>
+          <t>607878655</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>646467487</t>
+          <t>627964256</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>606989481</t>
+          <t>600969791</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -10216,11 +10216,7 @@
       <c r="O128" s="3" t="inlineStr"/>
       <c r="P128" s="3" t="inlineStr"/>
       <c r="Q128" s="3" t="inlineStr"/>
-      <c r="R128" s="3" t="inlineStr">
-        <is>
-          <t>658241465</t>
-        </is>
-      </c>
+      <c r="R128" s="3" t="inlineStr"/>
       <c r="S128" s="3" t="inlineStr">
         <is>
           <t>https://www.fraga.org</t>
@@ -11900,7 +11896,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>793097655</t>
+          <t>793186762</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12188,7 +12184,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>793094074</t>
+          <t>793183183</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -13047,7 +13043,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>641490590</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13205,7 +13201,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>626900413</t>
+          <t>606560616</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14539,152 +14535,152 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>MINI POWER POP FEST · PYRAMIDIACS + RADIO DAYS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Aclam Club</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>Pyramidiacs</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N186" s="3" t="inlineStr"/>
       <c r="O186" s="3" t="inlineStr"/>
-      <c r="P186" s="3" t="inlineStr"/>
-      <c r="Q186" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R186" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S186" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>Sergio Solís Gálvez</t>
+        </is>
+      </c>
+      <c r="Q186" s="3" t="inlineStr"/>
+      <c r="R186" s="3" t="inlineStr"/>
+      <c r="S186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Sala Upload - Poble Espanyol</t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chantada</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Nocturna Festival</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr"/>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr"/>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr">
-        <is>
-          <t>Sergio Solís Gálvez</t>
-        </is>
-      </c>
-      <c r="Q187" s="3" t="inlineStr"/>
-      <c r="R187" s="3" t="inlineStr"/>
-      <c r="S187" s="3" t="inlineStr"/>
+      <c r="P187" s="3" t="inlineStr"/>
+      <c r="Q187" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R187" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S187" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -15051,7 +15047,7 @@
       </c>
       <c r="R193" s="3" t="inlineStr">
         <is>
-          <t>616472692</t>
+          <t>880898509</t>
         </is>
       </c>
       <c r="S193" s="3" t="inlineStr">
@@ -15533,7 +15529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27/10/2026 09:43</t>
+          <t>28/10/2026 10:29</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>793186775</t>
+          <t>793274359</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>618380445</t>
+          <t>616064725</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -3276,11 +3276,7 @@
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>830184285</t>
-        </is>
-      </c>
+      <c r="R36" s="3" t="inlineStr"/>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4405,7 +4401,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>610733608</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4478,7 +4474,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>628006791</t>
+          <t>686165275</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -5836,7 +5832,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>793186775</t>
+          <t>793274359</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7332,7 +7328,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>627964256</t>
+          <t>642564266</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7583,7 +7579,7 @@
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>670715147</t>
+          <t>710091137</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr">
@@ -7932,7 +7928,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>600969791</t>
+          <t>606989481</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -10216,7 +10212,11 @@
       <c r="O128" s="3" t="inlineStr"/>
       <c r="P128" s="3" t="inlineStr"/>
       <c r="Q128" s="3" t="inlineStr"/>
-      <c r="R128" s="3" t="inlineStr"/>
+      <c r="R128" s="3" t="inlineStr">
+        <is>
+          <t>658241465</t>
+        </is>
+      </c>
       <c r="S128" s="3" t="inlineStr">
         <is>
           <t>https://www.fraga.org</t>
@@ -11896,7 +11896,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>793186762</t>
+          <t>793274346</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>793183183</t>
+          <t>793270765</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>674085843</t>
+          <t>685691226</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>730774212</t>
+          <t>610733608</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>606560616</t>
+          <t>626900413</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>674085843</t>
+          <t>685691226</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>618380445</t>
+          <t>616064725</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr">
@@ -14573,7 +14573,7 @@
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Pyramidiacs</t>
+          <t>Pyramidiacs, Radio Days</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr"/>
@@ -15529,7 +15529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28/10/2026 10:29</t>
+          <t>29/10/2026 10:48</t>
         </is>
       </c>
     </row>

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S200"/>
+  <dimension ref="A1:S201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>793274359</t>
+          <t>793360742</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>616064725</t>
+          <t>618380445</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>610733608</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>686165275</t>
+          <t>683372807</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -5832,7 +5832,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>793274359</t>
+          <t>793360742</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>642564266</t>
+          <t>609160509</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>733346966</t>
+          <t>694066444</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -11450,7 +11450,7 @@
       <c r="Q144" s="3" t="inlineStr"/>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>791536509</t>
+          <t>793271513</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr">
@@ -11896,7 +11896,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>793274346</t>
+          <t>793360728</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>793270765</t>
+          <t>793357150</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>685691226</t>
+          <t>654913226</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>610733608</t>
+          <t>730774212</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>626900413</t>
+          <t>606560616</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>685691226</t>
+          <t>654913226</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>616064725</t>
+          <t>618380445</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr">
@@ -14535,73 +14535,101 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>MINI POWER POP FEST · PYRAMIDIACS + RADIO DAYS</t>
+          <t>Castañazo Rock 2026</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Aclam Club</t>
+          <t>Mercado ganadero</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Chantada</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="G186" s="3" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr"/>
+          <t>Lugo</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Urbano, Pop, Rock, Punk</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>bajo</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>CUPIDO, JUNNIO, CANO</t>
+        </is>
+      </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Pyramidiacs, Radio Days</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr"/>
+          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>https://castanhazo.com/venda-de-entradas/</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>attcliente@woutick.es</t>
+        </is>
+      </c>
       <c r="O186" s="3" t="inlineStr"/>
-      <c r="P186" s="3" t="inlineStr">
-        <is>
-          <t>Sergio Solís Gálvez</t>
-        </is>
-      </c>
-      <c r="Q186" s="3" t="inlineStr"/>
-      <c r="R186" s="3" t="inlineStr"/>
-      <c r="S186" s="3" t="inlineStr"/>
+      <c r="P186" s="3" t="inlineStr"/>
+      <c r="Q186" s="3" t="inlineStr">
+        <is>
+          <t>concello@concellodechantada.es</t>
+        </is>
+      </c>
+      <c r="R186" s="3" t="inlineStr">
+        <is>
+          <t>614817558</t>
+        </is>
+      </c>
+      <c r="S186" s="3" t="inlineStr">
+        <is>
+          <t>https://www.concellodechantada.org</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Castañazo Rock 2026</t>
+          <t>Nocturna Festival</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -14611,76 +14639,48 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Mercado ganadero</t>
+          <t>Sala Upload - Poble Espanyol</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Chantada</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Lugo</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Urbano, Pop, Rock, Punk</t>
-        </is>
-      </c>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>alto</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>CUPIDO, JUNNIO, CANO</t>
-        </is>
-      </c>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Grande Amore, Kaotiko, Kumpania Algazarra, Moscow Death Brigade, Tremenda Jauría</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>https://castanhazo.com/venda-de-entradas/</t>
-        </is>
-      </c>
+          <t>Nocturna Festival</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
           <t>confirmado</t>
         </is>
       </c>
-      <c r="N187" s="3" t="inlineStr">
-        <is>
-          <t>attcliente@woutick.es</t>
-        </is>
-      </c>
+      <c r="N187" s="3" t="inlineStr"/>
       <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr"/>
-      <c r="Q187" s="3" t="inlineStr">
-        <is>
-          <t>concello@concellodechantada.es</t>
-        </is>
-      </c>
-      <c r="R187" s="3" t="inlineStr">
-        <is>
-          <t>614817558</t>
-        </is>
-      </c>
-      <c r="S187" s="3" t="inlineStr">
-        <is>
-          <t>https://www.concellodechantada.org</t>
-        </is>
-      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>Sergio Solís Gálvez</t>
+        </is>
+      </c>
+      <c r="Q187" s="3" t="inlineStr"/>
+      <c r="R187" s="3" t="inlineStr"/>
+      <c r="S187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -15384,32 +15384,32 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+          <t>Noah Kahan: Icónica Santalucia Sevilla Fest</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-07-07</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Varios Recintos</t>
+          <t>Plaza de España</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Seville</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr"/>
@@ -15422,7 +15422,7 @@
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Circuit Festival</t>
+          <t>Noah Kahan</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr"/>
@@ -15435,7 +15435,7 @@
       <c r="O199" s="3" t="inlineStr"/>
       <c r="P199" s="3" t="inlineStr">
         <is>
-          <t>Matinée 2000, SLU</t>
+          <t>Live Nation España S.A.U.</t>
         </is>
       </c>
       <c r="Q199" s="3" t="inlineStr"/>
@@ -15445,30 +15445,34 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Scanner bilbao</t>
+          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>D8 sorkuntza</t>
+          <t>Varios Recintos</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="4" t="inlineStr">
@@ -15477,7 +15481,11 @@
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
@@ -15488,15 +15496,68 @@
       <c r="O200" s="3" t="inlineStr"/>
       <c r="P200" s="3" t="inlineStr">
         <is>
-          <t>Copilots Events</t>
+          <t>Matinée 2000, SLU</t>
         </is>
       </c>
       <c r="Q200" s="3" t="inlineStr"/>
       <c r="R200" s="3" t="inlineStr"/>
       <c r="S200" s="3" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Scanner bilbao</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>D8 sorkuntza</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr"/>
+      <c r="O201" s="3" t="inlineStr"/>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>Copilots Events</t>
+        </is>
+      </c>
+      <c r="Q201" s="3" t="inlineStr"/>
+      <c r="R201" s="3" t="inlineStr"/>
+      <c r="S201" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S200"/>
+  <autoFilter ref="A1:S201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15529,7 +15590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29/10/2026 10:48</t>
+          <t>30/10/2026 10:48</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15601,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -15550,7 +15611,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -15627,7 +15688,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">

--- a/data/festivales.xlsx
+++ b/data/festivales.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Festivales'!$A$1:$S$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S201"/>
+  <dimension ref="A1:S202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2322,7 +2322,7 @@
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>793360742</t>
+          <t>793445284</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>644550455</t>
+          <t>647164776</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -3276,7 +3276,11 @@
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>648972706</t>
+        </is>
+      </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
           <t>https://www.ayto-torrejon.es</t>
@@ -4474,7 +4478,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>683372807</t>
+          <t>686165275</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -4636,7 +4640,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>644550455</t>
+          <t>647164776</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -5832,7 +5836,7 @@
       <c r="Q70" s="3" t="inlineStr"/>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>793360742</t>
+          <t>793445284</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -7328,7 +7332,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>609160509</t>
+          <t>615748574</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -7417,7 +7421,7 @@
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>873017920</t>
+          <t>719725401</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -7928,7 +7932,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>606989481</t>
+          <t>602598190</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -8305,7 +8309,7 @@
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>608100619</t>
+          <t>605698267</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr">
@@ -8686,7 +8690,7 @@
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>694066444</t>
+          <t>733346966</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -11896,7 +11900,7 @@
       <c r="Q150" s="3" t="inlineStr"/>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>793360728</t>
+          <t>793445274</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr">
@@ -12184,7 +12188,7 @@
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>793357150</t>
+          <t>793441690</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -12889,7 +12893,7 @@
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>654913226</t>
+          <t>685691226</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr">
@@ -13201,7 +13205,7 @@
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>606560616</t>
+          <t>626900413</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr">
@@ -14361,7 +14365,7 @@
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>654913226</t>
+          <t>685691226</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr">
@@ -14595,7 +14599,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>confirmado</t>
+          <t>por confirmar</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -15445,17 +15449,17 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>All Access Pass + Bus Super Early Bird - Circuit Festival 2027</t>
+          <t>All Access Pass First Release - Circuit Festival 2027</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-07</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>2027-08-15</t>
+          <t>2027-08-07</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -15506,30 +15510,34 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Scanner bilbao</t>
+          <t>Circuit Bus Wristband</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>2027-09-17</t>
+          <t>2027-08-15</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>D8 sorkuntza</t>
+          <t>Servicio Bus Circuit Festival</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Bilbao</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr"/>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr"/>
       <c r="I201" s="4" t="inlineStr">
@@ -15538,7 +15546,11 @@
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Festival</t>
+        </is>
+      </c>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
@@ -15549,15 +15561,68 @@
       <c r="O201" s="3" t="inlineStr"/>
       <c r="P201" s="3" t="inlineStr">
         <is>
-          <t>Copilots Events</t>
+          <t>Matinée 2000, SLU</t>
         </is>
       </c>
       <c r="Q201" s="3" t="inlineStr"/>
       <c r="R201" s="3" t="inlineStr"/>
       <c r="S201" s="3" t="inlineStr"/>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Scanner bilbao</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>2027-09-17</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>D8 sorkuntza</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>Bilbao</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr"/>
+      <c r="G202" s="3" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t>bajo</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>confirmado</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr"/>
+      <c r="O202" s="3" t="inlineStr"/>
+      <c r="P202" s="3" t="inlineStr">
+        <is>
+          <t>Copilots Events</t>
+        </is>
+      </c>
+      <c r="Q202" s="3" t="inlineStr"/>
+      <c r="R202" s="3" t="inlineStr"/>
+      <c r="S202" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S201"/>
+  <autoFilter ref="A1:S202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15590,7 +15655,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30/10/2026 10:48</t>
+          <t>31/10/2026 10:17</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15666,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
@@ -15698,7 +15763,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
